--- a/data/体检id.xlsx
+++ b/data/体检id.xlsx
@@ -1,25 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61CE318F-2945-401D-A08F-22A4FD2ACF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EEA8C199-0A1C-4A95-8B15-406790878663}"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -27,10 +18,9 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -81,7 +71,7 @@
     <t>pt217_ab42</t>
   </si>
   <si>
-    <t>cmbctid</t>
+    <t>evaluation_id</t>
   </si>
   <si>
     <t>陆奎珍</t>
@@ -1164,13 +1154,18 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1181,22 +1176,352 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1204,9 +1529,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1218,17 +1785,61 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1277,7 +1888,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1310,26 +1921,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1362,23 +1956,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1520,24 +2097,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15A4F0F9-DF09-42C8-B3BE-AFD3D18D66AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:O361"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="15" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1584,7 +2156,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -1619,19 +2191,19 @@
         <v>240.75</v>
       </c>
       <c r="L2" s="1">
-        <v>6.9740394999999997E-2</v>
+        <v>0.069740395</v>
       </c>
       <c r="M2" s="1">
-        <v>0.24299999999999999</v>
+        <v>0.243</v>
       </c>
       <c r="N2" s="1">
-        <v>1.4472901E-2</v>
+        <v>0.014472901</v>
       </c>
       <c r="O2" s="1">
         <v>179784</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -1666,19 +2238,19 @@
         <v>407.09</v>
       </c>
       <c r="L3" s="1">
-        <v>7.7329336999999998E-2</v>
+        <v>0.077329337</v>
       </c>
       <c r="M3" s="1">
-        <v>0.81100000000000005</v>
+        <v>0.811</v>
       </c>
       <c r="N3" s="1">
-        <v>2.5762389E-2</v>
+        <v>0.025762389</v>
       </c>
       <c r="O3" s="1">
         <v>179751</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -1713,19 +2285,19 @@
         <v>268.87</v>
       </c>
       <c r="L4" s="1">
-        <v>9.5250493000000006E-2</v>
+        <v>0.095250493</v>
       </c>
       <c r="M4" s="1">
         <v>0.107</v>
       </c>
       <c r="N4" s="1">
-        <v>4.178055E-3</v>
+        <v>0.004178055</v>
       </c>
       <c r="O4" s="1">
         <v>179798</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -1760,19 +2332,19 @@
         <v>274.23</v>
       </c>
       <c r="L5" s="1">
-        <v>7.4973561999999994E-2</v>
+        <v>0.074973562</v>
       </c>
       <c r="M5" s="1">
-        <v>0.34599999999999997</v>
+        <v>0.346</v>
       </c>
       <c r="N5" s="1">
-        <v>1.6828794000000001E-2</v>
+        <v>0.016828794</v>
       </c>
       <c r="O5" s="1">
         <v>179750</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15">
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
@@ -1807,19 +2379,19 @@
         <v>246.83</v>
       </c>
       <c r="L6" s="1">
-        <v>8.4228011000000005E-2</v>
+        <v>0.084228011</v>
       </c>
       <c r="M6" s="1">
-        <v>9.9000000000000005E-2</v>
+        <v>0.099</v>
       </c>
       <c r="N6" s="1">
-        <v>4.7619050000000003E-3</v>
+        <v>0.004761905</v>
       </c>
       <c r="O6" s="1">
         <v>179775</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -1854,19 +2426,19 @@
         <v>258.12</v>
       </c>
       <c r="L7" s="1">
-        <v>5.9236013999999997E-2</v>
+        <v>0.059236014</v>
       </c>
       <c r="M7" s="1">
-        <v>0.38400000000000001</v>
+        <v>0.384</v>
       </c>
       <c r="N7" s="1">
-        <v>2.5114454000000001E-2</v>
+        <v>0.025114454</v>
       </c>
       <c r="O7" s="1">
         <v>179773</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -1901,19 +2473,19 @@
         <v>345.54</v>
       </c>
       <c r="L8" s="1">
-        <v>7.4057996000000001E-2</v>
+        <v>0.074057996</v>
       </c>
       <c r="M8" s="1">
-        <v>0.19600000000000001</v>
+        <v>0.196</v>
       </c>
       <c r="N8" s="1">
-        <v>7.6592420000000001E-3</v>
+        <v>0.007659242</v>
       </c>
       <c r="O8" s="1">
         <v>179782</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15">
       <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
@@ -1948,19 +2520,19 @@
         <v>274.17</v>
       </c>
       <c r="L9" s="1">
-        <v>9.4029251999999994E-2</v>
+        <v>0.094029252</v>
       </c>
       <c r="M9" s="1">
-        <v>0.11600000000000001</v>
+        <v>0.116</v>
       </c>
       <c r="N9" s="1">
-        <v>4.4996120000000001E-3</v>
+        <v>0.004499612</v>
       </c>
       <c r="O9" s="1">
         <v>179757</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15">
       <c r="A10" s="1" t="s">
         <v>23</v>
       </c>
@@ -1992,19 +2564,19 @@
         <v>26.56</v>
       </c>
       <c r="K10" s="1">
-        <v>315.79000000000002</v>
+        <v>315.79</v>
       </c>
       <c r="L10" s="1">
-        <v>8.4106526000000001E-2</v>
+        <v>0.084106526</v>
       </c>
       <c r="M10" s="1">
-        <v>9.2999999999999999E-2</v>
+        <v>0.093</v>
       </c>
       <c r="N10" s="1">
-        <v>3.5015060000000001E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.003501506</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="1" t="s">
         <v>24</v>
       </c>
@@ -2039,19 +2611,19 @@
         <v>207.99</v>
       </c>
       <c r="L11" s="1">
-        <v>7.7599884999999993E-2</v>
+        <v>0.077599885</v>
       </c>
       <c r="M11" s="1">
-        <v>0.14599999999999999</v>
+        <v>0.146</v>
       </c>
       <c r="N11" s="1">
-        <v>9.0458489999999999E-3</v>
+        <v>0.009045849</v>
       </c>
       <c r="O11" s="1">
         <v>179783</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15">
       <c r="A12" s="1" t="s">
         <v>25</v>
       </c>
@@ -2083,22 +2655,22 @@
         <v>27.1</v>
       </c>
       <c r="K12" s="1">
-        <v>298.52999999999997</v>
+        <v>298.53</v>
       </c>
       <c r="L12" s="1">
-        <v>9.0778146000000004E-2</v>
+        <v>0.090778146</v>
       </c>
       <c r="M12" s="1">
-        <v>6.9000000000000006E-2</v>
+        <v>0.069</v>
       </c>
       <c r="N12" s="1">
-        <v>2.5461250000000002E-3</v>
+        <v>0.002546125</v>
       </c>
       <c r="O12" s="1">
         <v>179809</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15">
       <c r="A13" s="1" t="s">
         <v>26</v>
       </c>
@@ -2133,19 +2705,19 @@
         <v>266.17</v>
       </c>
       <c r="L13" s="1">
-        <v>9.1558027E-2</v>
+        <v>0.091558027</v>
       </c>
       <c r="M13" s="1">
-        <v>5.6000000000000001E-2</v>
+        <v>0.056</v>
       </c>
       <c r="N13" s="1">
-        <v>2.2979070000000001E-3</v>
+        <v>0.002297907</v>
       </c>
       <c r="O13" s="1">
         <v>179771</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15">
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
@@ -2180,19 +2752,19 @@
         <v>278.31</v>
       </c>
       <c r="L14" s="1">
-        <v>9.5864324000000001E-2</v>
+        <v>0.095864324</v>
       </c>
       <c r="M14" s="1">
-        <v>0.10299999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="N14" s="1">
-        <v>3.8605699999999998E-3</v>
+        <v>0.00386057</v>
       </c>
       <c r="O14" s="1">
         <v>179789</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15">
       <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
@@ -2227,19 +2799,19 @@
         <v>468.41</v>
       </c>
       <c r="L15" s="1">
-        <v>7.0835379000000004E-2</v>
+        <v>0.070835379</v>
       </c>
       <c r="M15" s="1">
-        <v>6.6000000000000003E-2</v>
+        <v>0.066</v>
       </c>
       <c r="N15" s="1">
-        <v>1.9891499999999999E-3</v>
+        <v>0.00198915</v>
       </c>
       <c r="O15" s="1">
         <v>179788</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15">
       <c r="A16" s="1" t="s">
         <v>29</v>
       </c>
@@ -2268,19 +2840,19 @@
         <v>273.64</v>
       </c>
       <c r="L16" s="1">
-        <v>9.7683087000000002E-2</v>
+        <v>0.097683087</v>
       </c>
       <c r="M16" s="1">
         <v>0.193</v>
       </c>
       <c r="N16" s="1">
-        <v>7.2203520000000002E-3</v>
+        <v>0.007220352</v>
       </c>
       <c r="O16" s="1">
         <v>179799</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15">
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
@@ -2315,19 +2887,19 @@
         <v>337.22</v>
       </c>
       <c r="L17" s="1">
-        <v>6.5921357E-2</v>
+        <v>0.065921357</v>
       </c>
       <c r="M17" s="1">
-        <v>0.79900000000000004</v>
+        <v>0.799</v>
       </c>
       <c r="N17" s="1">
-        <v>3.5942420000000003E-2</v>
+        <v>0.03594242</v>
       </c>
       <c r="O17" s="1">
         <v>179752</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15">
       <c r="A18" s="1" t="s">
         <v>31</v>
       </c>
@@ -2362,19 +2934,19 @@
         <v>243.22</v>
       </c>
       <c r="L18" s="1">
-        <v>9.6168078000000004E-2</v>
+        <v>0.096168078</v>
       </c>
       <c r="M18" s="1">
-        <v>8.3000000000000004E-2</v>
+        <v>0.083</v>
       </c>
       <c r="N18" s="1">
-        <v>3.5485249999999999E-3</v>
+        <v>0.003548525</v>
       </c>
       <c r="O18" s="1">
         <v>179749</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15">
       <c r="A19" s="1" t="s">
         <v>32</v>
       </c>
@@ -2409,19 +2981,19 @@
         <v>316.68</v>
       </c>
       <c r="L19" s="1">
-        <v>7.1744347999999999E-2</v>
+        <v>0.071744348</v>
       </c>
       <c r="M19" s="1">
-        <v>0.29599999999999999</v>
+        <v>0.296</v>
       </c>
       <c r="N19" s="1">
-        <v>1.3028168999999999E-2</v>
+        <v>0.013028169</v>
       </c>
       <c r="O19" s="1">
         <v>179881</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15">
       <c r="A20" s="1" t="s">
         <v>33</v>
       </c>
@@ -2456,19 +3028,19 @@
         <v>277.82</v>
       </c>
       <c r="L20" s="1">
-        <v>9.7617161999999993E-2</v>
+        <v>0.097617162</v>
       </c>
       <c r="M20" s="1">
-        <v>7.3999999999999996E-2</v>
+        <v>0.074</v>
       </c>
       <c r="N20" s="1">
-        <v>2.7286139999999999E-3</v>
+        <v>0.002728614</v>
       </c>
       <c r="O20" s="1">
         <v>179851</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15">
       <c r="A21" s="1" t="s">
         <v>34</v>
       </c>
@@ -2503,19 +3075,19 @@
         <v>206.6</v>
       </c>
       <c r="L21" s="1">
-        <v>9.8596321000000001E-2</v>
+        <v>0.098596321</v>
       </c>
       <c r="M21" s="1">
-        <v>9.7000000000000003E-2</v>
+        <v>0.097</v>
       </c>
       <c r="N21" s="1">
-        <v>4.7619050000000003E-3</v>
+        <v>0.004761905</v>
       </c>
       <c r="O21" s="1">
         <v>179855</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15">
       <c r="A22" s="1" t="s">
         <v>35</v>
       </c>
@@ -2544,25 +3116,25 @@
         <v>48</v>
       </c>
       <c r="J22" s="1">
-        <v>38.799999999999997</v>
+        <v>38.8</v>
       </c>
       <c r="K22" s="1">
         <v>463.93</v>
       </c>
       <c r="L22" s="1">
-        <v>8.3633307000000004E-2</v>
+        <v>0.083633307</v>
       </c>
       <c r="M22" s="1">
         <v>0.255</v>
       </c>
       <c r="N22" s="1">
-        <v>6.5721649999999996E-3</v>
+        <v>0.006572165</v>
       </c>
       <c r="O22" s="1">
         <v>179858</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15">
       <c r="A23" s="1" t="s">
         <v>36</v>
       </c>
@@ -2597,19 +3169,19 @@
         <v>236.98</v>
       </c>
       <c r="L23" s="1">
-        <v>8.9670014000000006E-2</v>
+        <v>0.089670014</v>
       </c>
       <c r="M23" s="1">
-        <v>7.9000000000000001E-2</v>
+        <v>0.079</v>
       </c>
       <c r="N23" s="1">
-        <v>3.7176470000000001E-3</v>
+        <v>0.003717647</v>
       </c>
       <c r="O23" s="1">
         <v>179862</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15">
       <c r="A24" s="1" t="s">
         <v>37</v>
       </c>
@@ -2644,19 +3216,19 @@
         <v>232.82</v>
       </c>
       <c r="L24" s="1">
-        <v>8.8523323000000001E-2</v>
+        <v>0.088523323</v>
       </c>
       <c r="M24" s="1">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="N24" s="1">
-        <v>3.3964099999999999E-3</v>
+        <v>0.00339641</v>
       </c>
       <c r="O24" s="1">
         <v>179873</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15">
       <c r="A25" s="1" t="s">
         <v>38</v>
       </c>
@@ -2688,19 +3260,19 @@
         <v>225.17</v>
       </c>
       <c r="L25" s="1">
-        <v>8.9709997E-2</v>
+        <v>0.089709997</v>
       </c>
       <c r="M25" s="1">
-        <v>6.5000000000000002E-2</v>
+        <v>0.065</v>
       </c>
       <c r="N25" s="1">
-        <v>3.217822E-3</v>
+        <v>0.003217822</v>
       </c>
       <c r="O25" s="1">
         <v>179883</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15">
       <c r="A26" s="1" t="s">
         <v>39</v>
       </c>
@@ -2732,19 +3304,19 @@
         <v>413.71</v>
       </c>
       <c r="L26" s="1">
-        <v>9.1706751000000003E-2</v>
+        <v>0.091706751</v>
       </c>
       <c r="M26" s="1">
-        <v>0.20599999999999999</v>
+        <v>0.206</v>
       </c>
       <c r="N26" s="1">
-        <v>5.4296259999999999E-3</v>
+        <v>0.005429626</v>
       </c>
       <c r="O26" s="1">
         <v>179818</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15">
       <c r="A27" s="1" t="s">
         <v>40</v>
       </c>
@@ -2779,19 +3351,19 @@
         <v>236.94</v>
       </c>
       <c r="L27" s="1">
-        <v>8.3523255000000005E-2</v>
+        <v>0.083523255</v>
       </c>
       <c r="M27" s="1">
-        <v>9.2999999999999999E-2</v>
+        <v>0.093</v>
       </c>
       <c r="N27" s="1">
-        <v>4.6993429999999999E-3</v>
+        <v>0.004699343</v>
       </c>
       <c r="O27" s="1">
         <v>179888</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15">
       <c r="A28" s="1" t="s">
         <v>41</v>
       </c>
@@ -2826,19 +3398,19 @@
         <v>253.25</v>
       </c>
       <c r="L28" s="1">
-        <v>9.0463968000000006E-2</v>
+        <v>0.090463968</v>
       </c>
       <c r="M28" s="1">
-        <v>7.9000000000000001E-2</v>
+        <v>0.079</v>
       </c>
       <c r="N28" s="1">
-        <v>3.4482760000000001E-3</v>
+        <v>0.003448276</v>
       </c>
       <c r="O28" s="1">
         <v>179870</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15">
       <c r="A29" s="1" t="s">
         <v>42</v>
       </c>
@@ -2873,19 +3445,19 @@
         <v>357.46</v>
       </c>
       <c r="L29" s="1">
-        <v>6.0230514999999998E-2</v>
+        <v>0.060230515</v>
       </c>
       <c r="M29" s="1">
         <v>0.68</v>
       </c>
       <c r="N29" s="1">
-        <v>3.1583836999999997E-2</v>
+        <v>0.031583837</v>
       </c>
       <c r="O29" s="1">
         <v>179846</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15">
       <c r="A30" s="1" t="s">
         <v>43</v>
       </c>
@@ -2920,19 +3492,19 @@
         <v>375.7</v>
       </c>
       <c r="L30" s="1">
-        <v>9.3665157999999998E-2</v>
+        <v>0.093665158</v>
       </c>
       <c r="M30" s="1">
-        <v>0.26800000000000002</v>
+        <v>0.268</v>
       </c>
       <c r="N30" s="1">
-        <v>7.6157999999999998E-3</v>
+        <v>0.0076158</v>
       </c>
       <c r="O30" s="1">
         <v>179894</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15">
       <c r="A31" s="1" t="s">
         <v>44</v>
       </c>
@@ -2967,19 +3539,19 @@
         <v>340.16</v>
       </c>
       <c r="L31" s="1">
-        <v>7.0202258000000003E-2</v>
+        <v>0.070202258</v>
       </c>
       <c r="M31" s="1">
-        <v>0.72499999999999998</v>
+        <v>0.725</v>
       </c>
       <c r="N31" s="1">
-        <v>3.0360134E-2</v>
+        <v>0.030360134</v>
       </c>
       <c r="O31" s="1">
         <v>179882</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15">
       <c r="A32" s="1" t="s">
         <v>45</v>
       </c>
@@ -3014,19 +3586,19 @@
         <v>271.14</v>
       </c>
       <c r="L32" s="1">
-        <v>8.6265397999999993E-2</v>
+        <v>0.086265398</v>
       </c>
       <c r="M32" s="1">
         <v>0.16</v>
       </c>
       <c r="N32" s="1">
-        <v>6.84053E-3</v>
+        <v>0.00684053</v>
       </c>
       <c r="O32" s="1">
         <v>179868</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15">
       <c r="A33" s="1" t="s">
         <v>46</v>
       </c>
@@ -3055,25 +3627,25 @@
         <v>36</v>
       </c>
       <c r="J33" s="1">
-        <v>19.420000000000002</v>
+        <v>19.42</v>
       </c>
       <c r="K33" s="1">
         <v>232.17</v>
       </c>
       <c r="L33" s="1">
-        <v>8.3645604999999998E-2</v>
+        <v>0.083645605</v>
       </c>
       <c r="M33" s="1">
-        <v>0.88100000000000001</v>
+        <v>0.881</v>
       </c>
       <c r="N33" s="1">
-        <v>4.5365601999999998E-2</v>
+        <v>0.045365602</v>
       </c>
       <c r="O33" s="1">
         <v>179860</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15">
       <c r="A34" s="1" t="s">
         <v>47</v>
       </c>
@@ -3108,19 +3680,19 @@
         <v>368.63</v>
       </c>
       <c r="L34" s="1">
-        <v>6.8741014000000003E-2</v>
+        <v>0.068741014</v>
       </c>
       <c r="M34" s="1">
         <v>0.24</v>
       </c>
       <c r="N34" s="1">
-        <v>9.4711919999999998E-3</v>
+        <v>0.009471192</v>
       </c>
       <c r="O34" s="1">
         <v>179875</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15">
       <c r="A35" s="1" t="s">
         <v>48</v>
       </c>
@@ -3149,25 +3721,25 @@
         <v>29</v>
       </c>
       <c r="J35" s="1">
-        <v>16.489999999999998</v>
+        <v>16.49</v>
       </c>
       <c r="K35" s="1">
         <v>244.27</v>
       </c>
       <c r="L35" s="1">
-        <v>6.7507266999999996E-2</v>
+        <v>0.067507267</v>
       </c>
       <c r="M35" s="1">
         <v>1.587</v>
       </c>
       <c r="N35" s="1">
-        <v>9.6240145999999999E-2</v>
+        <v>0.096240146</v>
       </c>
       <c r="O35" s="1">
         <v>179863</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15">
       <c r="A36" s="1" t="s">
         <v>49</v>
       </c>
@@ -3199,13 +3771,13 @@
         <v>0.08</v>
       </c>
       <c r="N36" s="1">
-        <v>3.0170000000000002E-3</v>
+        <v>0.003017</v>
       </c>
       <c r="O36" s="1">
         <v>80523</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15">
       <c r="A37" s="1" t="s">
         <v>50</v>
       </c>
@@ -3234,16 +3806,16 @@
         <v>0.105</v>
       </c>
       <c r="M37" s="1">
-        <v>0.88500000000000001</v>
+        <v>0.885</v>
       </c>
       <c r="N37" s="1">
-        <v>2.2803E-2</v>
+        <v>0.022803</v>
       </c>
       <c r="O37" s="1">
         <v>83925</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15">
       <c r="A38" s="1" t="s">
         <v>51</v>
       </c>
@@ -3266,16 +3838,16 @@
         <v>0.11</v>
       </c>
       <c r="M38" s="1">
-        <v>6.8000000000000005E-2</v>
+        <v>0.068</v>
       </c>
       <c r="N38" s="1">
-        <v>1.838E-3</v>
+        <v>0.001838</v>
       </c>
       <c r="O38" s="1">
         <v>83940</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15">
       <c r="A39" s="1" t="s">
         <v>52</v>
       </c>
@@ -3301,19 +3873,19 @@
         <v>32.5</v>
       </c>
       <c r="L39" s="1">
-        <v>0.10199999999999999</v>
+        <v>0.102</v>
       </c>
       <c r="M39" s="1">
-        <v>0.38300000000000001</v>
+        <v>0.383</v>
       </c>
       <c r="N39" s="1">
-        <v>1.1828E-2</v>
+        <v>0.011828</v>
       </c>
       <c r="O39" s="1">
         <v>80535</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15">
       <c r="A40" s="1" t="s">
         <v>53</v>
       </c>
@@ -3339,19 +3911,19 @@
         <v>50</v>
       </c>
       <c r="L40" s="1">
-        <v>7.8E-2</v>
+        <v>0.078</v>
       </c>
       <c r="M40" s="1">
-        <v>0.20599999999999999</v>
+        <v>0.206</v>
       </c>
       <c r="N40" s="1">
-        <v>8.5979999999999997E-3</v>
+        <v>0.008598</v>
       </c>
       <c r="O40" s="1">
         <v>81648</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15">
       <c r="A41" s="1" t="s">
         <v>54</v>
       </c>
@@ -3377,19 +3949,19 @@
         <v>35</v>
       </c>
       <c r="L41" s="1">
-        <v>8.4000000000000005E-2</v>
+        <v>0.084</v>
       </c>
       <c r="M41" s="1">
         <v>0.1</v>
       </c>
       <c r="N41" s="1">
-        <v>4.0679999999999996E-3</v>
+        <v>0.004068</v>
       </c>
       <c r="O41" s="1">
         <v>87008</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15">
       <c r="A42" s="1" t="s">
         <v>55</v>
       </c>
@@ -3415,19 +3987,19 @@
         <v>35</v>
       </c>
       <c r="L42" s="1">
-        <v>8.5000000000000006E-2</v>
+        <v>0.085</v>
       </c>
       <c r="M42" s="1">
-        <v>9.6000000000000002E-2</v>
+        <v>0.096</v>
       </c>
       <c r="N42" s="1">
-        <v>2.996E-3</v>
+        <v>0.002996</v>
       </c>
       <c r="O42" s="1">
         <v>86307</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15">
       <c r="A43" s="1" t="s">
         <v>56</v>
       </c>
@@ -3453,19 +4025,19 @@
         <v>33.75</v>
       </c>
       <c r="L43" s="1">
-        <v>9.6000000000000002E-2</v>
+        <v>0.096</v>
       </c>
       <c r="M43" s="1">
-        <v>9.2999999999999999E-2</v>
+        <v>0.093</v>
       </c>
       <c r="N43" s="1">
-        <v>3.323E-3</v>
+        <v>0.003323</v>
       </c>
       <c r="O43" s="1">
         <v>80528</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15">
       <c r="A44" s="1" t="s">
         <v>57</v>
       </c>
@@ -3497,13 +4069,13 @@
         <v>0.05</v>
       </c>
       <c r="N44" s="1">
-        <v>1.7949999999999999E-3</v>
+        <v>0.001795</v>
       </c>
       <c r="O44" s="1">
         <v>82212</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15">
       <c r="A45" s="1" t="s">
         <v>58</v>
       </c>
@@ -3529,19 +4101,19 @@
         <v>41.25</v>
       </c>
       <c r="L45" s="1">
-        <v>9.6000000000000002E-2</v>
+        <v>0.096</v>
       </c>
       <c r="M45" s="1">
-        <v>0.23100000000000001</v>
+        <v>0.231</v>
       </c>
       <c r="N45" s="1">
-        <v>7.9139999999999992E-3</v>
+        <v>0.007914</v>
       </c>
       <c r="O45" s="1">
         <v>80514</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15">
       <c r="A46" s="1" t="s">
         <v>59</v>
       </c>
@@ -3564,16 +4136,16 @@
         <v>0.104</v>
       </c>
       <c r="M46" s="1">
-        <v>0.20899999999999999</v>
+        <v>0.209</v>
       </c>
       <c r="N46" s="1">
-        <v>6.1929999999999997E-3</v>
+        <v>0.006193</v>
       </c>
       <c r="O46" s="1">
         <v>83939</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15">
       <c r="A47" s="1" t="s">
         <v>60</v>
       </c>
@@ -3599,19 +4171,19 @@
         <v>43.75</v>
       </c>
       <c r="L47" s="1">
-        <v>9.5000000000000001E-2</v>
+        <v>0.095</v>
       </c>
       <c r="M47" s="1">
-        <v>4.5999999999999999E-2</v>
+        <v>0.046</v>
       </c>
       <c r="N47" s="1">
-        <v>1.908E-3</v>
+        <v>0.001908</v>
       </c>
       <c r="O47" s="1">
         <v>86996</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15">
       <c r="A48" s="1" t="s">
         <v>61</v>
       </c>
@@ -3637,19 +4209,19 @@
         <v>47.5</v>
       </c>
       <c r="L48" s="1">
-        <v>7.6999999999999999E-2</v>
+        <v>0.077</v>
       </c>
       <c r="M48" s="1">
-        <v>0.14199999999999999</v>
+        <v>0.142</v>
       </c>
       <c r="N48" s="1">
-        <v>7.3839999999999999E-3</v>
+        <v>0.007384</v>
       </c>
       <c r="O48" s="1">
         <v>84407</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15">
       <c r="A49" s="1" t="s">
         <v>62</v>
       </c>
@@ -3675,19 +4247,19 @@
         <v>30</v>
       </c>
       <c r="L49" s="1">
-        <v>9.1999999999999998E-2</v>
+        <v>0.092</v>
       </c>
       <c r="M49" s="1">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="N49" s="1">
-        <v>5.3969999999999999E-3</v>
+        <v>0.005397</v>
       </c>
       <c r="O49" s="1">
         <v>86302</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15">
       <c r="A50" s="1" t="s">
         <v>63</v>
       </c>
@@ -3713,19 +4285,19 @@
         <v>26.25</v>
       </c>
       <c r="L50" s="1">
-        <v>0.10100000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="M50" s="1">
-        <v>9.2999999999999999E-2</v>
+        <v>0.093</v>
       </c>
       <c r="N50" s="1">
-        <v>2.967E-3</v>
+        <v>0.002967</v>
       </c>
       <c r="O50" s="1">
         <v>80580</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15">
       <c r="A51" s="1" t="s">
         <v>64</v>
       </c>
@@ -3757,13 +4329,13 @@
         <v>0.05</v>
       </c>
       <c r="N51" s="1">
-        <v>2.1389999999999998E-3</v>
+        <v>0.002139</v>
       </c>
       <c r="O51" s="1">
         <v>86929</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:15">
       <c r="A52" s="1" t="s">
         <v>65</v>
       </c>
@@ -3789,16 +4361,16 @@
         <v>36.25</v>
       </c>
       <c r="L52" s="1">
-        <v>8.8999999999999996E-2</v>
+        <v>0.089</v>
       </c>
       <c r="M52" s="1">
-        <v>4.4999999999999998E-2</v>
+        <v>0.045</v>
       </c>
       <c r="N52" s="1">
-        <v>1.97E-3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.00197</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
       <c r="A53" s="1" t="s">
         <v>66</v>
       </c>
@@ -3827,13 +4399,13 @@
         <v>0.03</v>
       </c>
       <c r="N53" s="1">
-        <v>2.0040000000000001E-3</v>
+        <v>0.002004</v>
       </c>
       <c r="O53" s="1">
         <v>85845</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15">
       <c r="A54" s="1" t="s">
         <v>67</v>
       </c>
@@ -3859,19 +4431,19 @@
         <v>28.75</v>
       </c>
       <c r="L54" s="1">
-        <v>9.4E-2</v>
+        <v>0.094</v>
       </c>
       <c r="M54" s="1">
-        <v>8.4000000000000005E-2</v>
+        <v>0.084</v>
       </c>
       <c r="N54" s="1">
-        <v>2.9499999999999999E-3</v>
+        <v>0.00295</v>
       </c>
       <c r="O54" s="1">
         <v>85824</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:15">
       <c r="A55" s="1" t="s">
         <v>68</v>
       </c>
@@ -3897,19 +4469,19 @@
         <v>36.25</v>
       </c>
       <c r="L55" s="1">
-        <v>8.7999999999999995E-2</v>
+        <v>0.088</v>
       </c>
       <c r="M55" s="1">
-        <v>4.9000000000000002E-2</v>
+        <v>0.049</v>
       </c>
       <c r="N55" s="1">
-        <v>1.7769999999999999E-3</v>
+        <v>0.001777</v>
       </c>
       <c r="O55" s="1">
         <v>82228</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15">
       <c r="A56" s="1" t="s">
         <v>69</v>
       </c>
@@ -3929,16 +4501,16 @@
         <v>45</v>
       </c>
       <c r="L56" s="1">
-        <v>9.6000000000000002E-2</v>
+        <v>0.096</v>
       </c>
       <c r="M56" s="1">
-        <v>7.1999999999999995E-2</v>
+        <v>0.072</v>
       </c>
       <c r="N56" s="1">
-        <v>2.9840000000000001E-3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.002984</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
       <c r="A57" s="1" t="s">
         <v>70</v>
       </c>
@@ -3961,19 +4533,19 @@
         <v>28.75</v>
       </c>
       <c r="L57" s="1">
-        <v>9.9000000000000005E-2</v>
+        <v>0.099</v>
       </c>
       <c r="M57" s="1">
-        <v>6.9000000000000006E-2</v>
+        <v>0.069</v>
       </c>
       <c r="N57" s="1">
-        <v>2.9650000000000002E-3</v>
+        <v>0.002965</v>
       </c>
       <c r="O57" s="1">
         <v>85851</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:15">
       <c r="A58" s="1" t="s">
         <v>71</v>
       </c>
@@ -3999,16 +4571,16 @@
         <v>38.75</v>
       </c>
       <c r="L58" s="1">
-        <v>0.11700000000000001</v>
+        <v>0.117</v>
       </c>
       <c r="M58" s="1">
-        <v>6.6000000000000003E-2</v>
+        <v>0.066</v>
       </c>
       <c r="N58" s="1">
-        <v>2.2769999999999999E-3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.002277</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15">
       <c r="A59" s="1" t="s">
         <v>72</v>
       </c>
@@ -4037,13 +4609,13 @@
         <v>0.105</v>
       </c>
       <c r="M59" s="1">
-        <v>6.0999999999999999E-2</v>
+        <v>0.061</v>
       </c>
       <c r="N59" s="1">
-        <v>1.8829999999999999E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.001883</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15">
       <c r="A60" s="1" t="s">
         <v>73</v>
       </c>
@@ -4069,19 +4641,19 @@
         <v>35</v>
       </c>
       <c r="L60" s="1">
-        <v>0.10199999999999999</v>
+        <v>0.102</v>
       </c>
       <c r="M60" s="1">
-        <v>5.1999999999999998E-2</v>
+        <v>0.052</v>
       </c>
       <c r="N60" s="1">
-        <v>1.9480000000000001E-3</v>
+        <v>0.001948</v>
       </c>
       <c r="O60" s="1">
         <v>81584</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15">
       <c r="A61" s="1" t="s">
         <v>74</v>
       </c>
@@ -4110,16 +4682,16 @@
         <v>0.09</v>
       </c>
       <c r="M61" s="1">
-        <v>7.1999999999999995E-2</v>
+        <v>0.072</v>
       </c>
       <c r="N61" s="1">
-        <v>3.248E-3</v>
+        <v>0.003248</v>
       </c>
       <c r="O61" s="1">
         <v>82223</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:15">
       <c r="A62" s="1" t="s">
         <v>75</v>
       </c>
@@ -4145,16 +4717,16 @@
         <v>38.75</v>
       </c>
       <c r="L62" s="1">
-        <v>0.26200000000000001</v>
+        <v>0.262</v>
       </c>
       <c r="M62" s="1">
-        <v>6.0220000000000002</v>
+        <v>6.022</v>
       </c>
       <c r="N62" s="1">
         <v>0.112183</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:15">
       <c r="A63" s="1" t="s">
         <v>76</v>
       </c>
@@ -4180,19 +4752,19 @@
         <v>25</v>
       </c>
       <c r="L63" s="1">
-        <v>6.3E-2</v>
+        <v>0.063</v>
       </c>
       <c r="M63" s="1">
         <v>0.254</v>
       </c>
       <c r="N63" s="1">
-        <v>1.3971000000000001E-2</v>
+        <v>0.013971</v>
       </c>
       <c r="O63" s="1">
         <v>85363</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:15">
       <c r="A64" s="1" t="s">
         <v>77</v>
       </c>
@@ -4218,19 +4790,19 @@
         <v>43.75</v>
       </c>
       <c r="L64" s="1">
-        <v>9.4E-2</v>
+        <v>0.094</v>
       </c>
       <c r="M64" s="1">
         <v>0.252</v>
       </c>
       <c r="N64" s="1">
-        <v>9.9129999999999999E-3</v>
+        <v>0.009913</v>
       </c>
       <c r="O64" s="1">
         <v>80511</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:15">
       <c r="A65" s="1" t="s">
         <v>78</v>
       </c>
@@ -4256,19 +4828,19 @@
         <v>31.25</v>
       </c>
       <c r="L65" s="1">
-        <v>7.8E-2</v>
+        <v>0.078</v>
       </c>
       <c r="M65" s="1">
-        <v>0.24199999999999999</v>
+        <v>0.242</v>
       </c>
       <c r="N65" s="1">
-        <v>9.9179999999999997E-3</v>
+        <v>0.009918</v>
       </c>
       <c r="O65" s="1">
         <v>82238</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:15">
       <c r="A66" s="1" t="s">
         <v>79</v>
       </c>
@@ -4294,19 +4866,19 @@
         <v>38.75</v>
       </c>
       <c r="L66" s="1">
-        <v>0.10199999999999999</v>
+        <v>0.102</v>
       </c>
       <c r="M66" s="1">
         <v>0.156</v>
       </c>
       <c r="N66" s="1">
-        <v>8.1119999999999994E-3</v>
+        <v>0.008112</v>
       </c>
       <c r="O66" s="1">
         <v>87000</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:15">
       <c r="A67" s="1" t="s">
         <v>80</v>
       </c>
@@ -4335,16 +4907,16 @@
         <v>0.112</v>
       </c>
       <c r="M67" s="1">
-        <v>0.13800000000000001</v>
+        <v>0.138</v>
       </c>
       <c r="N67" s="1">
-        <v>3.7880000000000001E-3</v>
+        <v>0.003788</v>
       </c>
       <c r="O67" s="1">
         <v>80552</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:15">
       <c r="A68" s="1" t="s">
         <v>81</v>
       </c>
@@ -4370,10 +4942,10 @@
         <v>0.03</v>
       </c>
       <c r="N68" s="1">
-        <v>1.686E-3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.001686</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
       <c r="A69" s="1" t="s">
         <v>82</v>
       </c>
@@ -4399,19 +4971,19 @@
         <v>35</v>
       </c>
       <c r="L69" s="1">
-        <v>8.4000000000000005E-2</v>
+        <v>0.084</v>
       </c>
       <c r="M69" s="1">
         <v>0.219</v>
       </c>
       <c r="N69" s="1">
-        <v>8.7039999999999999E-3</v>
+        <v>0.008704</v>
       </c>
       <c r="O69" s="1">
         <v>85828</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:15">
       <c r="A70" s="1" t="s">
         <v>83</v>
       </c>
@@ -4437,19 +5009,19 @@
         <v>37.5</v>
       </c>
       <c r="L70" s="1">
-        <v>0.10100000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="M70" s="1">
         <v>0.05</v>
       </c>
       <c r="N70" s="1">
-        <v>1.57E-3</v>
+        <v>0.00157</v>
       </c>
       <c r="O70" s="1">
         <v>81662</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:15">
       <c r="A71" s="1" t="s">
         <v>84</v>
       </c>
@@ -4475,19 +5047,19 @@
         <v>43.75</v>
       </c>
       <c r="L71" s="1">
-        <v>7.6999999999999999E-2</v>
+        <v>0.077</v>
       </c>
       <c r="M71" s="1">
-        <v>0.14099999999999999</v>
+        <v>0.141</v>
       </c>
       <c r="N71" s="1">
-        <v>6.1570000000000001E-3</v>
+        <v>0.006157</v>
       </c>
       <c r="O71" s="1">
         <v>82165</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:15">
       <c r="A72" s="1" t="s">
         <v>85</v>
       </c>
@@ -4510,19 +5082,19 @@
         <v>41.25</v>
       </c>
       <c r="L72" s="1">
-        <v>9.7000000000000003E-2</v>
+        <v>0.097</v>
       </c>
       <c r="M72" s="1">
-        <v>4.1000000000000002E-2</v>
+        <v>0.041</v>
       </c>
       <c r="N72" s="1">
-        <v>1.487E-3</v>
+        <v>0.001487</v>
       </c>
       <c r="O72" s="1">
         <v>85864</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:15">
       <c r="A73" s="1" t="s">
         <v>86</v>
       </c>
@@ -4548,19 +5120,19 @@
         <v>38.75</v>
       </c>
       <c r="L73" s="1">
-        <v>8.2000000000000003E-2</v>
+        <v>0.082</v>
       </c>
       <c r="M73" s="1">
         <v>0.127</v>
       </c>
       <c r="N73" s="1">
-        <v>5.587E-3</v>
+        <v>0.005587</v>
       </c>
       <c r="O73" s="1">
         <v>86349</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:15">
       <c r="A74" s="1" t="s">
         <v>87</v>
       </c>
@@ -4589,13 +5161,13 @@
         <v>0.03</v>
       </c>
       <c r="N74" s="1">
-        <v>1.2509999999999999E-3</v>
+        <v>0.001251</v>
       </c>
       <c r="O74" s="1">
         <v>85835</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:15">
       <c r="A75" s="1" t="s">
         <v>88</v>
       </c>
@@ -4621,19 +5193,19 @@
         <v>45</v>
       </c>
       <c r="L75" s="1">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="M75" s="1">
-        <v>0.14399999999999999</v>
+        <v>0.144</v>
       </c>
       <c r="N75" s="1">
-        <v>7.358E-3</v>
+        <v>0.007358</v>
       </c>
       <c r="O75" s="1">
         <v>81590</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:15">
       <c r="A76" s="1" t="s">
         <v>89</v>
       </c>
@@ -4659,19 +5231,19 @@
         <v>28.75</v>
       </c>
       <c r="L76" s="1">
-        <v>7.0999999999999994E-2</v>
+        <v>0.071</v>
       </c>
       <c r="M76" s="1">
         <v>0.125</v>
       </c>
       <c r="N76" s="1">
-        <v>5.4990000000000004E-3</v>
+        <v>0.005499</v>
       </c>
       <c r="O76" s="1">
         <v>84396</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:15">
       <c r="A77" s="1" t="s">
         <v>90</v>
       </c>
@@ -4697,16 +5269,16 @@
         <v>38.75</v>
       </c>
       <c r="L77" s="1">
-        <v>9.9000000000000005E-2</v>
+        <v>0.099</v>
       </c>
       <c r="M77" s="1">
-        <v>0.10100000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="N77" s="1">
-        <v>3.1939999999999998E-3</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.003194</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
       <c r="A78" s="1" t="s">
         <v>91</v>
       </c>
@@ -4732,19 +5304,19 @@
         <v>56.25</v>
       </c>
       <c r="L78" s="1">
-        <v>9.9000000000000005E-2</v>
+        <v>0.099</v>
       </c>
       <c r="M78" s="1">
-        <v>8.5000000000000006E-2</v>
+        <v>0.085</v>
       </c>
       <c r="N78" s="1">
-        <v>2.4550000000000002E-3</v>
+        <v>0.002455</v>
       </c>
       <c r="O78" s="1">
         <v>82234</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:15">
       <c r="A79" s="1" t="s">
         <v>92</v>
       </c>
@@ -4770,19 +5342,19 @@
         <v>42.5</v>
       </c>
       <c r="L79" s="1">
-        <v>8.6999999999999994E-2</v>
+        <v>0.087</v>
       </c>
       <c r="M79" s="1">
-        <v>8.3000000000000004E-2</v>
+        <v>0.083</v>
       </c>
       <c r="N79" s="1">
-        <v>3.1459999999999999E-3</v>
+        <v>0.003146</v>
       </c>
       <c r="O79" s="1">
         <v>82205</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:15">
       <c r="A80" s="1" t="s">
         <v>93</v>
       </c>
@@ -4808,19 +5380,19 @@
         <v>32.5</v>
       </c>
       <c r="L80" s="1">
-        <v>9.1999999999999998E-2</v>
+        <v>0.092</v>
       </c>
       <c r="M80" s="1">
-        <v>7.1999999999999995E-2</v>
+        <v>0.072</v>
       </c>
       <c r="N80" s="1">
-        <v>3.0660000000000001E-3</v>
+        <v>0.003066</v>
       </c>
       <c r="O80" s="1">
         <v>83968</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:15">
       <c r="A81" s="1" t="s">
         <v>94</v>
       </c>
@@ -4846,19 +5418,19 @@
         <v>35</v>
       </c>
       <c r="L81" s="1">
-        <v>9.7000000000000003E-2</v>
+        <v>0.097</v>
       </c>
       <c r="M81" s="1">
         <v>0.04</v>
       </c>
       <c r="N81" s="1">
-        <v>1.297E-3</v>
+        <v>0.001297</v>
       </c>
       <c r="O81" s="1">
         <v>80538</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:15">
       <c r="A82" s="1" t="s">
         <v>95</v>
       </c>
@@ -4887,16 +5459,16 @@
         <v>0.1</v>
       </c>
       <c r="M82" s="1">
-        <v>8.1000000000000003E-2</v>
+        <v>0.081</v>
       </c>
       <c r="N82" s="1">
-        <v>2.885E-3</v>
+        <v>0.002885</v>
       </c>
       <c r="O82" s="1">
         <v>85842</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:15">
       <c r="A83" s="1" t="s">
         <v>96</v>
       </c>
@@ -4922,16 +5494,16 @@
         <v>30</v>
       </c>
       <c r="L83" s="1">
-        <v>9.1999999999999998E-2</v>
+        <v>0.092</v>
       </c>
       <c r="M83" s="1">
         <v>0.08</v>
       </c>
       <c r="N83" s="1">
-        <v>3.094E-3</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.003094</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15">
       <c r="A84" s="1" t="s">
         <v>97</v>
       </c>
@@ -4963,13 +5535,13 @@
         <v>0.08</v>
       </c>
       <c r="N84" s="1">
-        <v>2.9550000000000002E-3</v>
+        <v>0.002955</v>
       </c>
       <c r="O84" s="1">
         <v>82232</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:15">
       <c r="A85" s="1" t="s">
         <v>98</v>
       </c>
@@ -4989,19 +5561,19 @@
         <v>40</v>
       </c>
       <c r="L85" s="1">
-        <v>9.9000000000000005E-2</v>
+        <v>0.099</v>
       </c>
       <c r="M85" s="1">
         <v>0.08</v>
       </c>
       <c r="N85" s="1">
-        <v>2.8400000000000001E-3</v>
+        <v>0.00284</v>
       </c>
       <c r="O85" s="1">
         <v>81651</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:15">
       <c r="A86" s="1" t="s">
         <v>99</v>
       </c>
@@ -5033,13 +5605,13 @@
         <v>0.03</v>
       </c>
       <c r="N86" s="1">
-        <v>1.673E-3</v>
+        <v>0.001673</v>
       </c>
       <c r="O86" s="1">
         <v>85428</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:15">
       <c r="A87" s="1" t="s">
         <v>100</v>
       </c>
@@ -5068,16 +5640,16 @@
         <v>0.107</v>
       </c>
       <c r="M87" s="1">
-        <v>6.8000000000000005E-2</v>
+        <v>0.068</v>
       </c>
       <c r="N87" s="1">
-        <v>2.8089999999999999E-3</v>
+        <v>0.002809</v>
       </c>
       <c r="O87" s="1">
         <v>86956</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:15">
       <c r="A88" s="1" t="s">
         <v>101</v>
       </c>
@@ -5106,16 +5678,16 @@
         <v>0.11</v>
       </c>
       <c r="M88" s="1">
-        <v>6.6000000000000003E-2</v>
+        <v>0.066</v>
       </c>
       <c r="N88" s="1">
-        <v>1.9350000000000001E-3</v>
+        <v>0.001935</v>
       </c>
       <c r="O88" s="1">
         <v>81626</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:15">
       <c r="A89" s="1" t="s">
         <v>102</v>
       </c>
@@ -5141,19 +5713,19 @@
         <v>33.75</v>
       </c>
       <c r="L89" s="1">
-        <v>9.0999999999999998E-2</v>
+        <v>0.091</v>
       </c>
       <c r="M89" s="1">
-        <v>6.2E-2</v>
+        <v>0.062</v>
       </c>
       <c r="N89" s="1">
-        <v>2.5509999999999999E-3</v>
+        <v>0.002551</v>
       </c>
       <c r="O89" s="1">
         <v>82241</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:15">
       <c r="A90" s="1" t="s">
         <v>103</v>
       </c>
@@ -5179,19 +5751,19 @@
         <v>32.5</v>
       </c>
       <c r="L90" s="1">
-        <v>6.9000000000000006E-2</v>
+        <v>0.069</v>
       </c>
       <c r="M90" s="1">
-        <v>0.38200000000000001</v>
+        <v>0.382</v>
       </c>
       <c r="N90" s="1">
-        <v>2.1533E-2</v>
+        <v>0.021533</v>
       </c>
       <c r="O90" s="1">
         <v>82200</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:15">
       <c r="A91" s="1" t="s">
         <v>104</v>
       </c>
@@ -5217,19 +5789,19 @@
         <v>28.75</v>
       </c>
       <c r="L91" s="1">
-        <v>9.6000000000000002E-2</v>
+        <v>0.096</v>
       </c>
       <c r="M91" s="1">
-        <v>5.8000000000000003E-2</v>
+        <v>0.058</v>
       </c>
       <c r="N91" s="1">
-        <v>2.4229999999999998E-3</v>
+        <v>0.002423</v>
       </c>
       <c r="O91" s="1">
         <v>85817</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:15">
       <c r="A92" s="1" t="s">
         <v>105</v>
       </c>
@@ -5258,16 +5830,16 @@
         <v>0.104</v>
       </c>
       <c r="M92" s="1">
-        <v>8.4000000000000005E-2</v>
+        <v>0.084</v>
       </c>
       <c r="N92" s="1">
-        <v>2.6150000000000001E-3</v>
+        <v>0.002615</v>
       </c>
       <c r="O92" s="1">
         <v>86324</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:15">
       <c r="A93" s="1" t="s">
         <v>106</v>
       </c>
@@ -5293,13 +5865,13 @@
         <v>0.08</v>
       </c>
       <c r="N93" s="1">
-        <v>3.075E-3</v>
+        <v>0.003075</v>
       </c>
       <c r="O93" s="1">
         <v>81607</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:15">
       <c r="A94" s="1" t="s">
         <v>107</v>
       </c>
@@ -5325,19 +5897,19 @@
         <v>35</v>
       </c>
       <c r="L94" s="1">
-        <v>0.10299999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="M94" s="1">
         <v>0.05</v>
       </c>
       <c r="N94" s="1">
-        <v>1.4920000000000001E-3</v>
+        <v>0.001492</v>
       </c>
       <c r="O94" s="1">
         <v>81619</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:15">
       <c r="A95" s="1" t="s">
         <v>108</v>
       </c>
@@ -5363,19 +5935,19 @@
         <v>45</v>
       </c>
       <c r="L95" s="1">
-        <v>9.7000000000000003E-2</v>
+        <v>0.097</v>
       </c>
       <c r="M95" s="1">
-        <v>4.2000000000000003E-2</v>
+        <v>0.042</v>
       </c>
       <c r="N95" s="1">
-        <v>1.6659999999999999E-3</v>
+        <v>0.001666</v>
       </c>
       <c r="O95" s="1">
         <v>85814</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:15">
       <c r="A96" s="1" t="s">
         <v>109</v>
       </c>
@@ -5395,19 +5967,19 @@
         <v>31.25</v>
       </c>
       <c r="L96" s="1">
-        <v>9.2999999999999999E-2</v>
+        <v>0.093</v>
       </c>
       <c r="M96" s="1">
         <v>0.03</v>
       </c>
       <c r="N96" s="1">
-        <v>1.33E-3</v>
+        <v>0.00133</v>
       </c>
       <c r="O96" s="1">
         <v>81657</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:15">
       <c r="A97" s="1" t="s">
         <v>110</v>
       </c>
@@ -5436,16 +6008,16 @@
         <v>0.08</v>
       </c>
       <c r="M97" s="1">
-        <v>0.10100000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="N97" s="1">
-        <v>5.0150000000000004E-3</v>
+        <v>0.005015</v>
       </c>
       <c r="O97" s="1">
         <v>85831</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:15">
       <c r="A98" s="1" t="s">
         <v>111</v>
       </c>
@@ -5477,13 +6049,13 @@
         <v>0.115</v>
       </c>
       <c r="N98" s="1">
-        <v>4.7109999999999999E-3</v>
+        <v>0.004711</v>
       </c>
       <c r="O98" s="1">
         <v>83923</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:15">
       <c r="A99" s="1" t="s">
         <v>112</v>
       </c>
@@ -5509,16 +6081,16 @@
         <v>35</v>
       </c>
       <c r="L99" s="1">
-        <v>8.6999999999999994E-2</v>
+        <v>0.087</v>
       </c>
       <c r="M99" s="1">
-        <v>0.10199999999999999</v>
+        <v>0.102</v>
       </c>
       <c r="N99" s="1">
-        <v>3.7650000000000001E-3</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.003765</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15">
       <c r="A100" s="1" t="s">
         <v>113</v>
       </c>
@@ -5544,19 +6116,19 @@
         <v>40</v>
       </c>
       <c r="L100" s="1">
-        <v>8.4000000000000005E-2</v>
+        <v>0.084</v>
       </c>
       <c r="M100" s="1">
-        <v>0.25700000000000001</v>
+        <v>0.257</v>
       </c>
       <c r="N100" s="1">
-        <v>9.8130000000000005E-3</v>
+        <v>0.009813</v>
       </c>
       <c r="O100" s="1">
         <v>85812</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:15">
       <c r="A101" s="1" t="s">
         <v>114</v>
       </c>
@@ -5582,19 +6154,19 @@
         <v>52.5</v>
       </c>
       <c r="L101" s="1">
-        <v>8.5999999999999993E-2</v>
+        <v>0.086</v>
       </c>
       <c r="M101" s="1">
-        <v>0.10100000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="N101" s="1">
-        <v>4.4380000000000001E-3</v>
+        <v>0.004438</v>
       </c>
       <c r="O101" s="1">
         <v>85852</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:15">
       <c r="A102" s="1" t="s">
         <v>115</v>
       </c>
@@ -5620,19 +6192,19 @@
         <v>43.75</v>
       </c>
       <c r="L102" s="1">
-        <v>9.1999999999999998E-2</v>
+        <v>0.092</v>
       </c>
       <c r="M102" s="1">
-        <v>7.2999999999999995E-2</v>
+        <v>0.073</v>
       </c>
       <c r="N102" s="1">
-        <v>2.6329999999999999E-3</v>
+        <v>0.002633</v>
       </c>
       <c r="O102" s="1">
         <v>83882</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:15">
       <c r="A103" s="1" t="s">
         <v>116</v>
       </c>
@@ -5661,16 +6233,16 @@
         <v>0.106</v>
       </c>
       <c r="M103" s="1">
-        <v>4.7E-2</v>
+        <v>0.047</v>
       </c>
       <c r="N103" s="1">
-        <v>1.598E-3</v>
+        <v>0.001598</v>
       </c>
       <c r="O103" s="1">
         <v>80543</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:15">
       <c r="A104" s="1" t="s">
         <v>117</v>
       </c>
@@ -5699,16 +6271,16 @@
         <v>0.108</v>
       </c>
       <c r="M104" s="1">
-        <v>4.4999999999999998E-2</v>
+        <v>0.045</v>
       </c>
       <c r="N104" s="1">
-        <v>1.4779999999999999E-3</v>
+        <v>0.001478</v>
       </c>
       <c r="O104" s="1">
         <v>84381</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:15">
       <c r="A105" s="1" t="s">
         <v>118</v>
       </c>
@@ -5740,13 +6312,13 @@
         <v>0.03</v>
       </c>
       <c r="N105" s="1">
-        <v>1.487E-3</v>
+        <v>0.001487</v>
       </c>
       <c r="O105" s="1">
         <v>86985</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:15">
       <c r="A106" s="1" t="s">
         <v>119</v>
       </c>
@@ -5772,19 +6344,19 @@
         <v>28.75</v>
       </c>
       <c r="L106" s="1">
-        <v>0.10299999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="M106" s="1">
         <v>0.123</v>
       </c>
       <c r="N106" s="1">
-        <v>3.2829999999999999E-3</v>
+        <v>0.003283</v>
       </c>
       <c r="O106" s="1">
         <v>86356</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:15">
       <c r="A107" s="1" t="s">
         <v>120</v>
       </c>
@@ -5813,16 +6385,16 @@
         <v>0.108</v>
       </c>
       <c r="M107" s="1">
-        <v>0.11700000000000001</v>
+        <v>0.117</v>
       </c>
       <c r="N107" s="1">
-        <v>2.6540000000000001E-3</v>
+        <v>0.002654</v>
       </c>
       <c r="O107" s="1">
         <v>86327</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:15">
       <c r="A108" s="1" t="s">
         <v>121</v>
       </c>
@@ -5848,19 +6420,19 @@
         <v>38.75</v>
       </c>
       <c r="L108" s="1">
-        <v>9.2999999999999999E-2</v>
+        <v>0.093</v>
       </c>
       <c r="M108" s="1">
         <v>0.105</v>
       </c>
       <c r="N108" s="1">
-        <v>3.8210000000000002E-3</v>
+        <v>0.003821</v>
       </c>
       <c r="O108" s="1">
         <v>81589</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:15">
       <c r="A109" s="1" t="s">
         <v>122</v>
       </c>
@@ -5880,19 +6452,19 @@
         <v>42.5</v>
       </c>
       <c r="L109" s="1">
-        <v>0.10299999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="M109" s="1">
-        <v>0.10199999999999999</v>
+        <v>0.102</v>
       </c>
       <c r="N109" s="1">
-        <v>2.9689999999999999E-3</v>
+        <v>0.002969</v>
       </c>
       <c r="O109" s="1">
         <v>83966</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:15">
       <c r="A110" s="1" t="s">
         <v>123</v>
       </c>
@@ -5918,19 +6490,19 @@
         <v>37.5</v>
       </c>
       <c r="L110" s="1">
-        <v>0.10100000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="M110" s="1">
-        <v>8.2000000000000003E-2</v>
+        <v>0.082</v>
       </c>
       <c r="N110" s="1">
-        <v>2.5230000000000001E-3</v>
+        <v>0.002523</v>
       </c>
       <c r="O110" s="1">
         <v>84411</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:15">
       <c r="A111" s="1" t="s">
         <v>124</v>
       </c>
@@ -5956,19 +6528,19 @@
         <v>28.75</v>
       </c>
       <c r="L111" s="1">
-        <v>0.11600000000000001</v>
+        <v>0.116</v>
       </c>
       <c r="M111" s="1">
         <v>0.08</v>
       </c>
       <c r="N111" s="1">
-        <v>3.287E-3</v>
+        <v>0.003287</v>
       </c>
       <c r="O111" s="1">
         <v>87016</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:15">
       <c r="A112" s="1" t="s">
         <v>125</v>
       </c>
@@ -5988,16 +6560,16 @@
         <v>33.75</v>
       </c>
       <c r="L112" s="1">
-        <v>9.5000000000000001E-2</v>
+        <v>0.095</v>
       </c>
       <c r="M112" s="1">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="N112" s="1">
-        <v>3.5249999999999999E-3</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.003525</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15">
       <c r="A113" s="1" t="s">
         <v>126</v>
       </c>
@@ -6023,16 +6595,16 @@
         <v>0.108</v>
       </c>
       <c r="M113" s="1">
-        <v>5.5E-2</v>
+        <v>0.055</v>
       </c>
       <c r="N113" s="1">
-        <v>2.1480000000000002E-3</v>
+        <v>0.002148</v>
       </c>
       <c r="O113" s="1">
         <v>85862</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:15">
       <c r="A114" s="1" t="s">
         <v>127</v>
       </c>
@@ -6055,19 +6627,19 @@
         <v>31.25</v>
       </c>
       <c r="L114" s="1">
-        <v>9.9000000000000005E-2</v>
+        <v>0.099</v>
       </c>
       <c r="M114" s="1">
-        <v>5.2999999999999999E-2</v>
+        <v>0.053</v>
       </c>
       <c r="N114" s="1">
-        <v>2.4060000000000002E-3</v>
+        <v>0.002406</v>
       </c>
       <c r="O114" s="1">
         <v>85871</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:15">
       <c r="A115" s="1" t="s">
         <v>128</v>
       </c>
@@ -6096,13 +6668,13 @@
         <v>0.109</v>
       </c>
       <c r="M115" s="1">
-        <v>5.1999999999999998E-2</v>
+        <v>0.052</v>
       </c>
       <c r="N115" s="1">
-        <v>1.949E-3</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.001949</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15">
       <c r="A116" s="1" t="s">
         <v>129</v>
       </c>
@@ -6131,16 +6703,16 @@
         <v>0.104</v>
       </c>
       <c r="M116" s="1">
-        <v>7.4999999999999997E-2</v>
+        <v>0.075</v>
       </c>
       <c r="N116" s="1">
-        <v>2.637E-3</v>
+        <v>0.002637</v>
       </c>
       <c r="O116" s="1">
         <v>82216</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:15">
       <c r="A117" s="1" t="s">
         <v>130</v>
       </c>
@@ -6166,19 +6738,19 @@
         <v>25</v>
       </c>
       <c r="L117" s="1">
-        <v>9.4E-2</v>
+        <v>0.094</v>
       </c>
       <c r="M117" s="1">
-        <v>0.47699999999999998</v>
+        <v>0.477</v>
       </c>
       <c r="N117" s="1">
-        <v>1.3424999999999999E-2</v>
+        <v>0.013425</v>
       </c>
       <c r="O117" s="1">
         <v>83905</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:15">
       <c r="A118" s="1" t="s">
         <v>131</v>
       </c>
@@ -6204,19 +6776,19 @@
         <v>43.75</v>
       </c>
       <c r="L118" s="1">
-        <v>9.2999999999999999E-2</v>
+        <v>0.093</v>
       </c>
       <c r="M118" s="1">
-        <v>8.1000000000000003E-2</v>
+        <v>0.081</v>
       </c>
       <c r="N118" s="1">
-        <v>2.944E-3</v>
+        <v>0.002944</v>
       </c>
       <c r="O118" s="1">
         <v>85831</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:15">
       <c r="A119" s="1" t="s">
         <v>132</v>
       </c>
@@ -6245,16 +6817,16 @@
         <v>0.104</v>
       </c>
       <c r="M119" s="1">
-        <v>4.5999999999999999E-2</v>
+        <v>0.046</v>
       </c>
       <c r="N119" s="1">
-        <v>1.3860000000000001E-3</v>
+        <v>0.001386</v>
       </c>
       <c r="O119" s="1">
         <v>84398</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:15">
       <c r="A120" s="1" t="s">
         <v>133</v>
       </c>
@@ -6283,16 +6855,16 @@
         <v>0.1</v>
       </c>
       <c r="M120" s="1">
-        <v>3.3000000000000002E-2</v>
+        <v>0.033</v>
       </c>
       <c r="N120" s="1">
-        <v>1.322E-3</v>
+        <v>0.001322</v>
       </c>
       <c r="O120" s="1">
         <v>86297</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:15">
       <c r="A121" s="1" t="s">
         <v>134</v>
       </c>
@@ -6321,10 +6893,10 @@
         <v>0.124</v>
       </c>
       <c r="N121" s="1">
-        <v>4.2189999999999997E-3</v>
-      </c>
-    </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.004219</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15">
       <c r="A122" s="1" t="s">
         <v>135</v>
       </c>
@@ -6350,19 +6922,19 @@
         <v>36.25</v>
       </c>
       <c r="L122" s="1">
-        <v>8.5000000000000006E-2</v>
+        <v>0.085</v>
       </c>
       <c r="M122" s="1">
         <v>0.115</v>
       </c>
       <c r="N122" s="1">
-        <v>5.0509999999999999E-3</v>
+        <v>0.005051</v>
       </c>
       <c r="O122" s="1">
         <v>85827</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:15">
       <c r="A123" s="1" t="s">
         <v>136</v>
       </c>
@@ -6388,19 +6960,19 @@
         <v>26.25</v>
       </c>
       <c r="L123" s="1">
-        <v>0.10100000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="M123" s="1">
-        <v>0.14299999999999999</v>
+        <v>0.143</v>
       </c>
       <c r="N123" s="1">
-        <v>4.2760000000000003E-3</v>
+        <v>0.004276</v>
       </c>
       <c r="O123" s="1">
         <v>86988</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:15">
       <c r="A124" s="1" t="s">
         <v>137</v>
       </c>
@@ -6426,19 +6998,19 @@
         <v>41.25</v>
       </c>
       <c r="L124" s="1">
-        <v>9.6000000000000002E-2</v>
+        <v>0.096</v>
       </c>
       <c r="M124" s="1">
         <v>0.105</v>
       </c>
       <c r="N124" s="1">
-        <v>3.8279999999999998E-3</v>
+        <v>0.003828</v>
       </c>
       <c r="O124" s="1">
         <v>85423</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:15">
       <c r="A125" s="1" t="s">
         <v>138</v>
       </c>
@@ -6458,19 +7030,19 @@
         <v>43.75</v>
       </c>
       <c r="L125" s="1">
-        <v>9.8000000000000004E-2</v>
+        <v>0.098</v>
       </c>
       <c r="M125" s="1">
-        <v>0.13500000000000001</v>
+        <v>0.135</v>
       </c>
       <c r="N125" s="1">
-        <v>4.7039999999999998E-3</v>
+        <v>0.004704</v>
       </c>
       <c r="O125" s="1">
         <v>81620</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:15">
       <c r="A126" s="1" t="s">
         <v>139</v>
       </c>
@@ -6496,19 +7068,19 @@
         <v>35</v>
       </c>
       <c r="L126" s="1">
-        <v>0.10199999999999999</v>
+        <v>0.102</v>
       </c>
       <c r="M126" s="1">
         <v>0.1</v>
       </c>
       <c r="N126" s="1">
-        <v>3.2269999999999998E-3</v>
+        <v>0.003227</v>
       </c>
       <c r="O126" s="1">
         <v>80527</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:15">
       <c r="A127" s="1" t="s">
         <v>140</v>
       </c>
@@ -6534,19 +7106,19 @@
         <v>43.75</v>
       </c>
       <c r="L127" s="1">
-        <v>8.8999999999999996E-2</v>
+        <v>0.089</v>
       </c>
       <c r="M127" s="1">
-        <v>9.8000000000000004E-2</v>
+        <v>0.098</v>
       </c>
       <c r="N127" s="1">
-        <v>3.9290000000000002E-3</v>
+        <v>0.003929</v>
       </c>
       <c r="O127" s="1">
         <v>84412</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:15">
       <c r="A128" s="1" t="s">
         <v>141</v>
       </c>
@@ -6572,19 +7144,19 @@
         <v>36.25</v>
       </c>
       <c r="L128" s="1">
-        <v>9.4E-2</v>
+        <v>0.094</v>
       </c>
       <c r="M128" s="1">
-        <v>9.6000000000000002E-2</v>
+        <v>0.096</v>
       </c>
       <c r="N128" s="1">
-        <v>3.225E-3</v>
+        <v>0.003225</v>
       </c>
       <c r="O128" s="1">
         <v>85825</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:15">
       <c r="A129" s="1" t="s">
         <v>142</v>
       </c>
@@ -6613,16 +7185,16 @@
         <v>0.105</v>
       </c>
       <c r="M129" s="1">
-        <v>7.2999999999999995E-2</v>
+        <v>0.073</v>
       </c>
       <c r="N129" s="1">
-        <v>2.8839999999999998E-3</v>
+        <v>0.002884</v>
       </c>
       <c r="O129" s="1">
         <v>84405</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:15">
       <c r="A130" s="1" t="s">
         <v>143</v>
       </c>
@@ -6651,16 +7223,16 @@
         <v>0.113</v>
       </c>
       <c r="M130" s="1">
-        <v>6.8000000000000005E-2</v>
+        <v>0.068</v>
       </c>
       <c r="N130" s="1">
-        <v>2.4169999999999999E-3</v>
+        <v>0.002417</v>
       </c>
       <c r="O130" s="1">
         <v>86312</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:15">
       <c r="A131" s="1" t="s">
         <v>144</v>
       </c>
@@ -6686,19 +7258,19 @@
         <v>40</v>
       </c>
       <c r="L131" s="1">
-        <v>9.7000000000000003E-2</v>
+        <v>0.097</v>
       </c>
       <c r="M131" s="1">
-        <v>6.8000000000000005E-2</v>
+        <v>0.068</v>
       </c>
       <c r="N131" s="1">
-        <v>2.2729999999999998E-3</v>
+        <v>0.002273</v>
       </c>
       <c r="O131" s="1">
         <v>80512</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:15">
       <c r="A132" s="1" t="s">
         <v>145</v>
       </c>
@@ -6721,19 +7293,19 @@
         <v>36.25</v>
       </c>
       <c r="L132" s="1">
-        <v>0.10299999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="M132" s="1">
-        <v>5.6000000000000001E-2</v>
+        <v>0.056</v>
       </c>
       <c r="N132" s="1">
-        <v>2.5309999999999998E-3</v>
+        <v>0.002531</v>
       </c>
       <c r="O132" s="1">
         <v>85860</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:15">
       <c r="A133" s="1" t="s">
         <v>146</v>
       </c>
@@ -6756,19 +7328,19 @@
         <v>32.5</v>
       </c>
       <c r="L133" s="1">
-        <v>0.11700000000000001</v>
+        <v>0.117</v>
       </c>
       <c r="M133" s="1">
-        <v>5.3999999999999999E-2</v>
+        <v>0.054</v>
       </c>
       <c r="N133" s="1">
-        <v>1.9239999999999999E-3</v>
+        <v>0.001924</v>
       </c>
       <c r="O133" s="1">
         <v>85841</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:15">
       <c r="A134" s="1" t="s">
         <v>147</v>
       </c>
@@ -6797,16 +7369,16 @@
         <v>0.104</v>
       </c>
       <c r="M134" s="1">
-        <v>3.9E-2</v>
+        <v>0.039</v>
       </c>
       <c r="N134" s="1">
-        <v>1.6670000000000001E-3</v>
+        <v>0.001667</v>
       </c>
       <c r="O134" s="1">
         <v>83910</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:15">
       <c r="A135" s="1" t="s">
         <v>148</v>
       </c>
@@ -6826,19 +7398,19 @@
         <v>40</v>
       </c>
       <c r="L135" s="1">
-        <v>8.6999999999999994E-2</v>
+        <v>0.087</v>
       </c>
       <c r="M135" s="1">
-        <v>3.5999999999999997E-2</v>
+        <v>0.036</v>
       </c>
       <c r="N135" s="1">
-        <v>1.7600000000000001E-3</v>
+        <v>0.00176</v>
       </c>
       <c r="O135" s="1">
         <v>81615</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:15">
       <c r="A136" s="1" t="s">
         <v>149</v>
       </c>
@@ -6867,16 +7439,16 @@
         <v>0.105</v>
       </c>
       <c r="M136" s="1">
-        <v>3.9E-2</v>
+        <v>0.039</v>
       </c>
       <c r="N136" s="1">
-        <v>1.343E-3</v>
+        <v>0.001343</v>
       </c>
       <c r="O136" s="1">
         <v>85362</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:15">
       <c r="A137" s="1" t="s">
         <v>150</v>
       </c>
@@ -6902,19 +7474,19 @@
         <v>43.75</v>
       </c>
       <c r="L137" s="1">
-        <v>7.3999999999999996E-2</v>
+        <v>0.074</v>
       </c>
       <c r="M137" s="1">
-        <v>0.45500000000000002</v>
+        <v>0.455</v>
       </c>
       <c r="N137" s="1">
-        <v>2.3847E-2</v>
+        <v>0.023847</v>
       </c>
       <c r="O137" s="1">
         <v>83919</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:15">
       <c r="A138" s="1" t="s">
         <v>151</v>
       </c>
@@ -6940,19 +7512,19 @@
         <v>36.25</v>
       </c>
       <c r="L138" s="1">
-        <v>8.8999999999999996E-2</v>
+        <v>0.089</v>
       </c>
       <c r="M138" s="1">
         <v>0.112</v>
       </c>
       <c r="N138" s="1">
-        <v>4.7619999999999997E-3</v>
+        <v>0.004762</v>
       </c>
       <c r="O138" s="1">
         <v>80525</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:15">
       <c r="A139" s="1" t="s">
         <v>152</v>
       </c>
@@ -6972,19 +7544,19 @@
         <v>30</v>
       </c>
       <c r="L139" s="1">
-        <v>9.2999999999999999E-2</v>
+        <v>0.093</v>
       </c>
       <c r="M139" s="1">
         <v>0.154</v>
       </c>
       <c r="N139" s="1">
-        <v>5.496E-3</v>
+        <v>0.005496</v>
       </c>
       <c r="O139" s="1">
         <v>81640</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:15">
       <c r="A140" s="1" t="s">
         <v>153</v>
       </c>
@@ -7010,16 +7582,16 @@
         <v>42.5</v>
       </c>
       <c r="L140" s="1">
-        <v>8.6999999999999994E-2</v>
+        <v>0.087</v>
       </c>
       <c r="M140" s="1">
         <v>0.121</v>
       </c>
       <c r="N140" s="1">
-        <v>5.3629999999999997E-3</v>
-      </c>
-    </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.005363</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15">
       <c r="A141" s="1" t="s">
         <v>154</v>
       </c>
@@ -7045,16 +7617,16 @@
         <v>48.75</v>
       </c>
       <c r="L141" s="1">
-        <v>9.4E-2</v>
+        <v>0.094</v>
       </c>
       <c r="M141" s="1">
-        <v>0.10100000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="N141" s="1">
-        <v>3.594E-3</v>
-      </c>
-    </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.003594</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15">
       <c r="A142" s="1" t="s">
         <v>155</v>
       </c>
@@ -7074,19 +7646,19 @@
         <v>47.5</v>
       </c>
       <c r="L142" s="1">
-        <v>9.6000000000000002E-2</v>
+        <v>0.096</v>
       </c>
       <c r="M142" s="1">
-        <v>8.5999999999999993E-2</v>
+        <v>0.086</v>
       </c>
       <c r="N142" s="1">
-        <v>3.1900000000000001E-3</v>
+        <v>0.00319</v>
       </c>
       <c r="O142" s="1">
         <v>83930</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:15">
       <c r="A143" s="1" t="s">
         <v>156</v>
       </c>
@@ -7112,19 +7684,19 @@
         <v>36.25</v>
       </c>
       <c r="L143" s="1">
-        <v>0.11899999999999999</v>
+        <v>0.119</v>
       </c>
       <c r="M143" s="1">
         <v>0.08</v>
       </c>
       <c r="N143" s="1">
-        <v>2.392E-3</v>
+        <v>0.002392</v>
       </c>
       <c r="O143" s="1">
         <v>82199</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:15">
       <c r="A144" s="1" t="s">
         <v>157</v>
       </c>
@@ -7147,16 +7719,16 @@
         <v>0.107</v>
       </c>
       <c r="M144" s="1">
-        <v>5.7000000000000002E-2</v>
+        <v>0.057</v>
       </c>
       <c r="N144" s="1">
-        <v>2.0270000000000002E-3</v>
+        <v>0.002027</v>
       </c>
       <c r="O144" s="1">
         <v>82202</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:15">
       <c r="A145" s="1" t="s">
         <v>158</v>
       </c>
@@ -7182,16 +7754,16 @@
         <v>35</v>
       </c>
       <c r="L145" s="1">
-        <v>7.9000000000000001E-2</v>
+        <v>0.079</v>
       </c>
       <c r="M145" s="1">
-        <v>5.1999999999999998E-2</v>
+        <v>0.052</v>
       </c>
       <c r="N145" s="1">
-        <v>2.6289999999999998E-3</v>
-      </c>
-    </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.002629</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15">
       <c r="A146" s="1" t="s">
         <v>159</v>
       </c>
@@ -7217,16 +7789,16 @@
         <v>47.5</v>
       </c>
       <c r="L146" s="1">
-        <v>8.5999999999999993E-2</v>
+        <v>0.086</v>
       </c>
       <c r="M146" s="1">
-        <v>3.5999999999999997E-2</v>
+        <v>0.036</v>
       </c>
       <c r="N146" s="1">
-        <v>1.353E-3</v>
-      </c>
-    </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.001353</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15">
       <c r="A147" s="1" t="s">
         <v>160</v>
       </c>
@@ -7252,19 +7824,19 @@
         <v>45</v>
       </c>
       <c r="L147" s="1">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="M147" s="1">
-        <v>0.10100000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="N147" s="1">
-        <v>3.081E-3</v>
+        <v>0.003081</v>
       </c>
       <c r="O147" s="1">
         <v>81631</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:15">
       <c r="A148" s="1" t="s">
         <v>161</v>
       </c>
@@ -7290,19 +7862,19 @@
         <v>33.75</v>
       </c>
       <c r="L148" s="1">
-        <v>8.5999999999999993E-2</v>
+        <v>0.086</v>
       </c>
       <c r="M148" s="1">
-        <v>9.6000000000000002E-2</v>
+        <v>0.096</v>
       </c>
       <c r="N148" s="1">
-        <v>4.6579999999999998E-3</v>
+        <v>0.004658</v>
       </c>
       <c r="O148" s="1">
         <v>84423</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:15">
       <c r="A149" s="1" t="s">
         <v>162</v>
       </c>
@@ -7328,16 +7900,16 @@
         <v>31.25</v>
       </c>
       <c r="L149" s="1">
-        <v>9.2999999999999999E-2</v>
+        <v>0.093</v>
       </c>
       <c r="M149" s="1">
-        <v>8.3000000000000004E-2</v>
+        <v>0.083</v>
       </c>
       <c r="N149" s="1">
-        <v>2.7420000000000001E-3</v>
-      </c>
-    </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.002742</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15">
       <c r="A150" s="1" t="s">
         <v>163</v>
       </c>
@@ -7366,13 +7938,13 @@
         <v>0.09</v>
       </c>
       <c r="M150" s="1">
-        <v>7.4999999999999997E-2</v>
+        <v>0.075</v>
       </c>
       <c r="N150" s="1">
-        <v>2.8400000000000001E-3</v>
-      </c>
-    </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.00284</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15">
       <c r="A151" s="1" t="s">
         <v>164</v>
       </c>
@@ -7401,16 +7973,16 @@
         <v>0.105</v>
       </c>
       <c r="M151" s="1">
-        <v>6.4000000000000001E-2</v>
+        <v>0.064</v>
       </c>
       <c r="N151" s="1">
-        <v>2.0530000000000001E-3</v>
+        <v>0.002053</v>
       </c>
       <c r="O151" s="1">
         <v>85414</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:15">
       <c r="A152" s="1" t="s">
         <v>165</v>
       </c>
@@ -7436,19 +8008,19 @@
         <v>41.25</v>
       </c>
       <c r="L152" s="1">
-        <v>9.5000000000000001E-2</v>
+        <v>0.095</v>
       </c>
       <c r="M152" s="1">
-        <v>5.5E-2</v>
+        <v>0.055</v>
       </c>
       <c r="N152" s="1">
-        <v>1.861E-3</v>
+        <v>0.001861</v>
       </c>
       <c r="O152" s="1">
         <v>85413</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:15">
       <c r="A153" s="1" t="s">
         <v>166</v>
       </c>
@@ -7474,19 +8046,19 @@
         <v>27.5</v>
       </c>
       <c r="L153" s="1">
-        <v>9.9000000000000005E-2</v>
+        <v>0.099</v>
       </c>
       <c r="M153" s="1">
-        <v>4.9000000000000002E-2</v>
+        <v>0.049</v>
       </c>
       <c r="N153" s="1">
-        <v>1.8400000000000001E-3</v>
+        <v>0.00184</v>
       </c>
       <c r="O153" s="1">
         <v>83908</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:15">
       <c r="A154" s="1" t="s">
         <v>167</v>
       </c>
@@ -7512,19 +8084,19 @@
         <v>36.25</v>
       </c>
       <c r="L154" s="1">
-        <v>9.9000000000000005E-2</v>
+        <v>0.099</v>
       </c>
       <c r="M154" s="1">
-        <v>4.5999999999999999E-2</v>
+        <v>0.046</v>
       </c>
       <c r="N154" s="1">
-        <v>1.8439999999999999E-3</v>
+        <v>0.001844</v>
       </c>
       <c r="O154" s="1">
         <v>84392</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:15">
       <c r="A155" s="1" t="s">
         <v>168</v>
       </c>
@@ -7556,13 +8128,13 @@
         <v>0.106</v>
       </c>
       <c r="N155" s="1">
-        <v>3.359E-3</v>
+        <v>0.003359</v>
       </c>
       <c r="O155" s="1">
         <v>80542</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:15">
       <c r="A156" s="1" t="s">
         <v>169</v>
       </c>
@@ -7588,19 +8160,19 @@
         <v>33.75</v>
       </c>
       <c r="L156" s="1">
-        <v>9.4E-2</v>
+        <v>0.094</v>
       </c>
       <c r="M156" s="1">
-        <v>6.8000000000000005E-2</v>
+        <v>0.068</v>
       </c>
       <c r="N156" s="1">
-        <v>2.82E-3</v>
+        <v>0.00282</v>
       </c>
       <c r="O156" s="1">
         <v>85813</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:15">
       <c r="A157" s="1" t="s">
         <v>170</v>
       </c>
@@ -7626,19 +8198,19 @@
         <v>33.75</v>
       </c>
       <c r="L157" s="1">
-        <v>8.4000000000000005E-2</v>
+        <v>0.084</v>
       </c>
       <c r="M157" s="1">
         <v>0.3</v>
       </c>
       <c r="N157" s="1">
-        <v>9.0419999999999997E-3</v>
+        <v>0.009042</v>
       </c>
       <c r="O157" s="1">
         <v>81673</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:15">
       <c r="A158" s="1" t="s">
         <v>171</v>
       </c>
@@ -7664,19 +8236,19 @@
         <v>28.75</v>
       </c>
       <c r="L158" s="1">
-        <v>9.1999999999999998E-2</v>
+        <v>0.092</v>
       </c>
       <c r="M158" s="1">
         <v>0.1</v>
       </c>
       <c r="N158" s="1">
-        <v>4.3080000000000002E-3</v>
+        <v>0.004308</v>
       </c>
       <c r="O158" s="1">
         <v>84406</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:15">
       <c r="A159" s="1" t="s">
         <v>172</v>
       </c>
@@ -7705,16 +8277,16 @@
         <v>0.112</v>
       </c>
       <c r="M159" s="1">
-        <v>9.0999999999999998E-2</v>
+        <v>0.091</v>
       </c>
       <c r="N159" s="1">
-        <v>2.7179999999999999E-3</v>
+        <v>0.002718</v>
       </c>
       <c r="O159" s="1">
         <v>83881</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:15">
       <c r="A160" s="1" t="s">
         <v>173</v>
       </c>
@@ -7743,16 +8315,16 @@
         <v>0.193</v>
       </c>
       <c r="M160" s="1">
-        <v>8.5999999999999993E-2</v>
+        <v>0.086</v>
       </c>
       <c r="N160" s="1">
-        <v>1.6199999999999999E-3</v>
+        <v>0.00162</v>
       </c>
       <c r="O160" s="1">
         <v>85397</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:15">
       <c r="A161" s="1" t="s">
         <v>174</v>
       </c>
@@ -7778,19 +8350,19 @@
         <v>42.5</v>
       </c>
       <c r="L161" s="1">
-        <v>8.4000000000000005E-2</v>
+        <v>0.084</v>
       </c>
       <c r="M161" s="1">
-        <v>0.46800000000000003</v>
+        <v>0.468</v>
       </c>
       <c r="N161" s="1">
-        <v>1.3965999999999999E-2</v>
+        <v>0.013966</v>
       </c>
       <c r="O161" s="1">
         <v>86933</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:15">
       <c r="A162" s="1" t="s">
         <v>175</v>
       </c>
@@ -7816,16 +8388,16 @@
         <v>48.75</v>
       </c>
       <c r="L162" s="1">
-        <v>8.6999999999999994E-2</v>
+        <v>0.087</v>
       </c>
       <c r="M162" s="1">
-        <v>6.4000000000000001E-2</v>
+        <v>0.064</v>
       </c>
       <c r="N162" s="1">
-        <v>2.611E-3</v>
-      </c>
-    </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.002611</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15">
       <c r="A163" s="1" t="s">
         <v>176</v>
       </c>
@@ -7848,19 +8420,19 @@
         <v>66.25</v>
       </c>
       <c r="L163" s="1">
-        <v>9.8000000000000004E-2</v>
+        <v>0.098</v>
       </c>
       <c r="M163" s="1">
-        <v>5.1999999999999998E-2</v>
+        <v>0.052</v>
       </c>
       <c r="N163" s="1">
-        <v>2.271E-3</v>
+        <v>0.002271</v>
       </c>
       <c r="O163" s="1">
         <v>85870</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:15">
       <c r="A164" s="1" t="s">
         <v>177</v>
       </c>
@@ -7886,19 +8458,19 @@
         <v>67.5</v>
       </c>
       <c r="L164" s="1">
-        <v>7.9000000000000001E-2</v>
+        <v>0.079</v>
       </c>
       <c r="M164" s="1">
-        <v>0.48899999999999999</v>
+        <v>0.489</v>
       </c>
       <c r="N164" s="1">
-        <v>1.9229E-2</v>
+        <v>0.019229</v>
       </c>
       <c r="O164" s="1">
         <v>86311</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:15">
       <c r="A165" s="1" t="s">
         <v>178</v>
       </c>
@@ -7927,13 +8499,13 @@
         <v>0.09</v>
       </c>
       <c r="M165" s="1">
-        <v>7.6999999999999999E-2</v>
+        <v>0.077</v>
       </c>
       <c r="N165" s="1">
-        <v>3.2299999999999998E-3</v>
-      </c>
-    </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.00323</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15">
       <c r="A166" s="1" t="s">
         <v>179</v>
       </c>
@@ -7959,19 +8531,19 @@
         <v>42.5</v>
       </c>
       <c r="L166" s="1">
-        <v>9.9000000000000005E-2</v>
+        <v>0.099</v>
       </c>
       <c r="M166" s="1">
-        <v>4.2000000000000003E-2</v>
+        <v>0.042</v>
       </c>
       <c r="N166" s="1">
-        <v>1.9810000000000001E-3</v>
+        <v>0.001981</v>
       </c>
       <c r="O166" s="1">
         <v>81658</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:15">
       <c r="A167" s="1" t="s">
         <v>180</v>
       </c>
@@ -8003,13 +8575,13 @@
         <v>0.311</v>
       </c>
       <c r="N167" s="1">
-        <v>1.4465E-2</v>
+        <v>0.014465</v>
       </c>
       <c r="O167" s="1">
         <v>86950</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:15">
       <c r="A168" s="1" t="s">
         <v>181</v>
       </c>
@@ -8035,19 +8607,19 @@
         <v>43.75</v>
       </c>
       <c r="L168" s="1">
-        <v>8.1000000000000003E-2</v>
+        <v>0.081</v>
       </c>
       <c r="M168" s="1">
         <v>0.188</v>
       </c>
       <c r="N168" s="1">
-        <v>5.2209999999999999E-3</v>
+        <v>0.005221</v>
       </c>
       <c r="O168" s="1">
         <v>85400</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:15">
       <c r="A169" s="1" t="s">
         <v>182</v>
       </c>
@@ -8079,13 +8651,13 @@
         <v>0.432</v>
       </c>
       <c r="N169" s="1">
-        <v>2.1861999999999999E-2</v>
+        <v>0.021862</v>
       </c>
       <c r="O169" s="1">
         <v>82206</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:15">
       <c r="A170" s="1" t="s">
         <v>183</v>
       </c>
@@ -8111,19 +8683,19 @@
         <v>47.5</v>
       </c>
       <c r="L170" s="1">
-        <v>8.3000000000000004E-2</v>
+        <v>0.083</v>
       </c>
       <c r="M170" s="1">
-        <v>0.22700000000000001</v>
+        <v>0.227</v>
       </c>
       <c r="N170" s="1">
-        <v>7.79E-3</v>
+        <v>0.00779</v>
       </c>
       <c r="O170" s="1">
         <v>86989</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:15">
       <c r="A171" s="1" t="s">
         <v>184</v>
       </c>
@@ -8149,19 +8721,19 @@
         <v>32.5</v>
       </c>
       <c r="L171" s="1">
-        <v>9.7000000000000003E-2</v>
+        <v>0.097</v>
       </c>
       <c r="M171" s="1">
-        <v>6.4000000000000001E-2</v>
+        <v>0.064</v>
       </c>
       <c r="N171" s="1">
-        <v>3.1819999999999999E-3</v>
+        <v>0.003182</v>
       </c>
       <c r="O171" s="1">
         <v>83927</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:15">
       <c r="A172" s="1" t="s">
         <v>185</v>
       </c>
@@ -8187,19 +8759,19 @@
         <v>50</v>
       </c>
       <c r="L172" s="1">
-        <v>9.8000000000000004E-2</v>
+        <v>0.098</v>
       </c>
       <c r="M172" s="1">
         <v>0.247</v>
       </c>
       <c r="N172" s="1">
-        <v>7.2750000000000002E-3</v>
+        <v>0.007275</v>
       </c>
       <c r="O172" s="1">
         <v>86342</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:15">
       <c r="A173" s="1" t="s">
         <v>186</v>
       </c>
@@ -8225,16 +8797,16 @@
         <v>28.75</v>
       </c>
       <c r="L173" s="1">
-        <v>8.3000000000000004E-2</v>
+        <v>0.083</v>
       </c>
       <c r="M173" s="1">
-        <v>0.13400000000000001</v>
+        <v>0.134</v>
       </c>
       <c r="N173" s="1">
-        <v>6.2849999999999998E-3</v>
-      </c>
-    </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.006285</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15">
       <c r="A174" s="1" t="s">
         <v>187</v>
       </c>
@@ -8254,19 +8826,19 @@
         <v>43.75</v>
       </c>
       <c r="L174" s="1">
-        <v>8.7999999999999995E-2</v>
+        <v>0.088</v>
       </c>
       <c r="M174" s="1">
-        <v>0.34300000000000003</v>
+        <v>0.343</v>
       </c>
       <c r="N174" s="1">
-        <v>9.273E-3</v>
+        <v>0.009273</v>
       </c>
       <c r="O174" s="1">
         <v>86935</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:15">
       <c r="A175" s="1" t="s">
         <v>176</v>
       </c>
@@ -8292,19 +8864,19 @@
         <v>48.75</v>
       </c>
       <c r="L175" s="1">
-        <v>9.0999999999999998E-2</v>
+        <v>0.091</v>
       </c>
       <c r="M175" s="1">
-        <v>0.16600000000000001</v>
+        <v>0.166</v>
       </c>
       <c r="N175" s="1">
-        <v>5.561E-3</v>
+        <v>0.005561</v>
       </c>
       <c r="O175" s="1">
         <v>85364</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:15">
       <c r="A176" s="1" t="s">
         <v>188</v>
       </c>
@@ -8330,16 +8902,16 @@
         <v>43.75</v>
       </c>
       <c r="L176" s="1">
-        <v>6.7000000000000004E-2</v>
+        <v>0.067</v>
       </c>
       <c r="M176" s="1">
-        <v>0.20799999999999999</v>
+        <v>0.208</v>
       </c>
       <c r="N176" s="1">
-        <v>9.9089999999999994E-3</v>
-      </c>
-    </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.009909</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15">
       <c r="A177" s="1" t="s">
         <v>189</v>
       </c>
@@ -8359,19 +8931,19 @@
         <v>40</v>
       </c>
       <c r="L177" s="1">
-        <v>9.7000000000000003E-2</v>
+        <v>0.097</v>
       </c>
       <c r="M177" s="1">
-        <v>3.7999999999999999E-2</v>
+        <v>0.038</v>
       </c>
       <c r="N177" s="1">
-        <v>1.3470000000000001E-3</v>
+        <v>0.001347</v>
       </c>
       <c r="O177" s="1">
         <v>86343</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:15">
       <c r="A178" s="1" t="s">
         <v>190</v>
       </c>
@@ -8400,16 +8972,16 @@
         <v>0.1</v>
       </c>
       <c r="M178" s="1">
-        <v>5.6000000000000001E-2</v>
+        <v>0.056</v>
       </c>
       <c r="N178" s="1">
-        <v>2.1199999999999999E-3</v>
+        <v>0.00212</v>
       </c>
       <c r="O178" s="1">
         <v>83883</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:15">
       <c r="A179" s="1" t="s">
         <v>191</v>
       </c>
@@ -8435,19 +9007,19 @@
         <v>25</v>
       </c>
       <c r="L179" s="1">
-        <v>0.10299999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="M179" s="1">
-        <v>5.3999999999999999E-2</v>
+        <v>0.054</v>
       </c>
       <c r="N179" s="1">
-        <v>1.8760000000000001E-3</v>
+        <v>0.001876</v>
       </c>
       <c r="O179" s="1">
         <v>81616</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:15">
       <c r="A180" s="1" t="s">
         <v>192</v>
       </c>
@@ -8476,16 +9048,16 @@
         <v>0.106</v>
       </c>
       <c r="M180" s="1">
-        <v>6.9000000000000006E-2</v>
+        <v>0.069</v>
       </c>
       <c r="N180" s="1">
-        <v>3.8660000000000001E-3</v>
+        <v>0.003866</v>
       </c>
       <c r="O180" s="1">
         <v>85854</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:15">
       <c r="A181" s="1" t="s">
         <v>193</v>
       </c>
@@ -8511,16 +9083,16 @@
         <v>28.75</v>
       </c>
       <c r="L181" s="1">
-        <v>9.5000000000000001E-2</v>
+        <v>0.095</v>
       </c>
       <c r="M181" s="1">
-        <v>6.0999999999999999E-2</v>
+        <v>0.061</v>
       </c>
       <c r="N181" s="1">
-        <v>2.2000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.0022</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15">
       <c r="A182" s="1" t="s">
         <v>194</v>
       </c>
@@ -8546,19 +9118,19 @@
         <v>30</v>
       </c>
       <c r="L182" s="1">
-        <v>9.6000000000000002E-2</v>
+        <v>0.096</v>
       </c>
       <c r="M182" s="1">
         <v>0.104</v>
       </c>
       <c r="N182" s="1">
-        <v>4.1729999999999996E-3</v>
+        <v>0.004173</v>
       </c>
       <c r="O182" s="1">
         <v>86938</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:15">
       <c r="A183" s="1" t="s">
         <v>195</v>
       </c>
@@ -8581,13 +9153,13 @@
         <v>0.08</v>
       </c>
       <c r="M183" s="1">
-        <v>0.27600000000000002</v>
+        <v>0.276</v>
       </c>
       <c r="N183" s="1">
-        <v>1.1349E-2</v>
-      </c>
-    </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.011349</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15">
       <c r="A184" s="1" t="s">
         <v>196</v>
       </c>
@@ -8613,19 +9185,19 @@
         <v>37.5</v>
       </c>
       <c r="L184" s="1">
-        <v>9.1999999999999998E-2</v>
+        <v>0.092</v>
       </c>
       <c r="M184" s="1">
-        <v>0.41799999999999998</v>
+        <v>0.418</v>
       </c>
       <c r="N184" s="1">
-        <v>1.4619999999999999E-2</v>
+        <v>0.01462</v>
       </c>
       <c r="O184" s="1">
         <v>81683</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:15">
       <c r="A185" s="1" t="s">
         <v>197</v>
       </c>
@@ -8654,13 +9226,13 @@
         <v>0.114</v>
       </c>
       <c r="M185" s="1">
-        <v>0.20100000000000001</v>
+        <v>0.201</v>
       </c>
       <c r="N185" s="1">
-        <v>4.9839999999999997E-3</v>
-      </c>
-    </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.004984</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15">
       <c r="A186" s="1" t="s">
         <v>198</v>
       </c>
@@ -8683,16 +9255,16 @@
         <v>0.11</v>
       </c>
       <c r="M186" s="1">
-        <v>6.6000000000000003E-2</v>
+        <v>0.066</v>
       </c>
       <c r="N186" s="1">
-        <v>3.277E-3</v>
+        <v>0.003277</v>
       </c>
       <c r="O186" s="1">
         <v>83952</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:15">
       <c r="A187" s="1" t="s">
         <v>199</v>
       </c>
@@ -8718,19 +9290,19 @@
         <v>37.5</v>
       </c>
       <c r="L187" s="1">
-        <v>0.10100000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="M187" s="1">
-        <v>9.1999999999999998E-2</v>
+        <v>0.092</v>
       </c>
       <c r="N187" s="1">
-        <v>2.8900000000000002E-3</v>
+        <v>0.00289</v>
       </c>
       <c r="O187" s="1">
         <v>83909</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:15">
       <c r="A188" s="1" t="s">
         <v>200</v>
       </c>
@@ -8756,19 +9328,19 @@
         <v>33.75</v>
       </c>
       <c r="L188" s="1">
-        <v>7.4999999999999997E-2</v>
+        <v>0.075</v>
       </c>
       <c r="M188" s="1">
-        <v>0.17799999999999999</v>
+        <v>0.178</v>
       </c>
       <c r="N188" s="1">
-        <v>8.4880000000000008E-3</v>
+        <v>0.008488</v>
       </c>
       <c r="O188" s="1">
         <v>86403</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:15">
       <c r="A189" s="1" t="s">
         <v>201</v>
       </c>
@@ -8794,19 +9366,19 @@
         <v>32.5</v>
       </c>
       <c r="L189" s="1">
-        <v>6.0999999999999999E-2</v>
+        <v>0.061</v>
       </c>
       <c r="M189" s="1">
-        <v>0.60699999999999998</v>
+        <v>0.607</v>
       </c>
       <c r="N189" s="1">
-        <v>1.5066E-2</v>
+        <v>0.015066</v>
       </c>
       <c r="O189" s="1">
         <v>84395</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:15">
       <c r="A190" s="1" t="s">
         <v>202</v>
       </c>
@@ -8832,19 +9404,19 @@
         <v>37.5</v>
       </c>
       <c r="L190" s="1">
-        <v>9.2999999999999999E-2</v>
+        <v>0.093</v>
       </c>
       <c r="M190" s="1">
-        <v>0.17599999999999999</v>
+        <v>0.176</v>
       </c>
       <c r="N190" s="1">
-        <v>6.1240000000000001E-3</v>
+        <v>0.006124</v>
       </c>
       <c r="O190" s="1">
         <v>81652</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:15">
       <c r="A191" s="1" t="s">
         <v>203</v>
       </c>
@@ -8870,19 +9442,19 @@
         <v>33.75</v>
       </c>
       <c r="L191" s="1">
-        <v>8.7999999999999995E-2</v>
+        <v>0.088</v>
       </c>
       <c r="M191" s="1">
-        <v>7.6999999999999999E-2</v>
+        <v>0.077</v>
       </c>
       <c r="N191" s="1">
-        <v>3.797E-3</v>
+        <v>0.003797</v>
       </c>
       <c r="O191" s="1">
         <v>83907</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:15">
       <c r="A192" s="1" t="s">
         <v>204</v>
       </c>
@@ -8908,16 +9480,16 @@
         <v>52.5</v>
       </c>
       <c r="L192" s="1">
-        <v>9.0999999999999998E-2</v>
+        <v>0.091</v>
       </c>
       <c r="M192" s="1">
-        <v>0.11600000000000001</v>
+        <v>0.116</v>
       </c>
       <c r="N192" s="1">
-        <v>3.7829999999999999E-3</v>
-      </c>
-    </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.003783</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15">
       <c r="A193" s="1" t="s">
         <v>205</v>
       </c>
@@ -8943,19 +9515,19 @@
         <v>43.75</v>
       </c>
       <c r="L193" s="1">
-        <v>7.9000000000000001E-2</v>
+        <v>0.079</v>
       </c>
       <c r="M193" s="1">
-        <v>8.1000000000000003E-2</v>
+        <v>0.081</v>
       </c>
       <c r="N193" s="1">
-        <v>2.5899999999999999E-3</v>
+        <v>0.00259</v>
       </c>
       <c r="O193" s="1">
         <v>80497</v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:15">
       <c r="A194" s="1" t="s">
         <v>206</v>
       </c>
@@ -8981,19 +9553,19 @@
         <v>43.75</v>
       </c>
       <c r="L194" s="1">
-        <v>7.3999999999999996E-2</v>
+        <v>0.074</v>
       </c>
       <c r="M194" s="1">
-        <v>0.20799999999999999</v>
+        <v>0.208</v>
       </c>
       <c r="N194" s="1">
-        <v>8.9040000000000005E-3</v>
+        <v>0.008904</v>
       </c>
       <c r="O194" s="1">
         <v>86328</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:15">
       <c r="A195" s="1" t="s">
         <v>207</v>
       </c>
@@ -9019,19 +9591,19 @@
         <v>41.25</v>
       </c>
       <c r="L195" s="1">
-        <v>9.1999999999999998E-2</v>
+        <v>0.092</v>
       </c>
       <c r="M195" s="1">
-        <v>7.6999999999999999E-2</v>
+        <v>0.077</v>
       </c>
       <c r="N195" s="1">
-        <v>3.156E-3</v>
+        <v>0.003156</v>
       </c>
       <c r="O195" s="1">
         <v>80561</v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:15">
       <c r="A196" s="1" t="s">
         <v>208</v>
       </c>
@@ -9057,19 +9629,19 @@
         <v>32.5</v>
       </c>
       <c r="L196" s="1">
-        <v>9.1999999999999998E-2</v>
+        <v>0.092</v>
       </c>
       <c r="M196" s="1">
-        <v>7.8E-2</v>
+        <v>0.078</v>
       </c>
       <c r="N196" s="1">
-        <v>3.2160000000000001E-3</v>
+        <v>0.003216</v>
       </c>
       <c r="O196" s="1">
         <v>83889</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:15">
       <c r="A197" s="1" t="s">
         <v>209</v>
       </c>
@@ -9095,19 +9667,19 @@
         <v>30</v>
       </c>
       <c r="L197" s="1">
-        <v>9.7000000000000003E-2</v>
+        <v>0.097</v>
       </c>
       <c r="M197" s="1">
-        <v>7.0999999999999994E-2</v>
+        <v>0.071</v>
       </c>
       <c r="N197" s="1">
-        <v>2.8310000000000002E-3</v>
+        <v>0.002831</v>
       </c>
       <c r="O197" s="1">
         <v>86966</v>
       </c>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:15">
       <c r="A198" s="1" t="s">
         <v>210</v>
       </c>
@@ -9139,13 +9711,13 @@
         <v>0.09</v>
       </c>
       <c r="N198" s="1">
-        <v>4.2230000000000002E-3</v>
+        <v>0.004223</v>
       </c>
       <c r="O198" s="1">
         <v>85810</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:15">
       <c r="A199" s="1" t="s">
         <v>211</v>
       </c>
@@ -9174,16 +9746,16 @@
         <v>0.106</v>
       </c>
       <c r="M199" s="1">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="N199" s="1">
-        <v>2.5490000000000001E-3</v>
+        <v>0.002549</v>
       </c>
       <c r="O199" s="1">
         <v>85352</v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:15">
       <c r="A200" s="1" t="s">
         <v>212</v>
       </c>
@@ -9209,19 +9781,19 @@
         <v>42.5</v>
       </c>
       <c r="L200" s="1">
-        <v>8.4000000000000005E-2</v>
+        <v>0.084</v>
       </c>
       <c r="M200" s="1">
-        <v>5.0999999999999997E-2</v>
+        <v>0.051</v>
       </c>
       <c r="N200" s="1">
-        <v>2.7729999999999999E-3</v>
+        <v>0.002773</v>
       </c>
       <c r="O200" s="1">
         <v>86371</v>
       </c>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:15">
       <c r="A201" s="1" t="s">
         <v>213</v>
       </c>
@@ -9247,16 +9819,16 @@
         <v>0.107</v>
       </c>
       <c r="M201" s="1">
-        <v>3.7999999999999999E-2</v>
+        <v>0.038</v>
       </c>
       <c r="N201" s="1">
-        <v>1.5690000000000001E-3</v>
+        <v>0.001569</v>
       </c>
       <c r="O201" s="1">
         <v>85398</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:15">
       <c r="A202" s="1" t="s">
         <v>214</v>
       </c>
@@ -9282,19 +9854,19 @@
         <v>40</v>
       </c>
       <c r="L202" s="1">
-        <v>0.10100000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="M202" s="1">
-        <v>5.7000000000000002E-2</v>
+        <v>0.057</v>
       </c>
       <c r="N202" s="1">
-        <v>2.1310000000000001E-3</v>
+        <v>0.002131</v>
       </c>
       <c r="O202" s="1">
         <v>80509</v>
       </c>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:15">
       <c r="A203" s="1" t="s">
         <v>215</v>
       </c>
@@ -9320,19 +9892,19 @@
         <v>31.25</v>
       </c>
       <c r="L203" s="1">
-        <v>8.6999999999999994E-2</v>
+        <v>0.087</v>
       </c>
       <c r="M203" s="1">
-        <v>4.8000000000000001E-2</v>
+        <v>0.048</v>
       </c>
       <c r="N203" s="1">
-        <v>2.3119999999999998E-3</v>
+        <v>0.002312</v>
       </c>
       <c r="O203" s="1">
         <v>83963</v>
       </c>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:15">
       <c r="A204" s="1" t="s">
         <v>216</v>
       </c>
@@ -9355,19 +9927,19 @@
         <v>48.75</v>
       </c>
       <c r="L204" s="1">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="M204" s="1">
-        <v>6.6000000000000003E-2</v>
+        <v>0.066</v>
       </c>
       <c r="N204" s="1">
-        <v>2.8089999999999999E-3</v>
+        <v>0.002809</v>
       </c>
       <c r="O204" s="1">
         <v>85417</v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:15">
       <c r="A205" s="1" t="s">
         <v>217</v>
       </c>
@@ -9393,19 +9965,19 @@
         <v>53.75</v>
       </c>
       <c r="L205" s="1">
-        <v>9.5000000000000001E-2</v>
+        <v>0.095</v>
       </c>
       <c r="M205" s="1">
-        <v>6.0999999999999999E-2</v>
+        <v>0.061</v>
       </c>
       <c r="N205" s="1">
-        <v>2.562E-3</v>
+        <v>0.002562</v>
       </c>
       <c r="O205" s="1">
         <v>82195</v>
       </c>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:15">
       <c r="A206" s="1" t="s">
         <v>218</v>
       </c>
@@ -9431,16 +10003,16 @@
         <v>48.75</v>
       </c>
       <c r="L206" s="1">
-        <v>8.5000000000000006E-2</v>
+        <v>0.085</v>
       </c>
       <c r="M206" s="1">
-        <v>0.54900000000000004</v>
+        <v>0.549</v>
       </c>
       <c r="N206" s="1">
-        <v>1.8717999999999999E-2</v>
-      </c>
-    </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.018718</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15">
       <c r="A207" s="1" t="s">
         <v>219</v>
       </c>
@@ -9460,19 +10032,19 @@
         <v>26.25</v>
       </c>
       <c r="L207" s="1">
-        <v>9.5000000000000001E-2</v>
+        <v>0.095</v>
       </c>
       <c r="M207" s="1">
-        <v>0.26200000000000001</v>
+        <v>0.262</v>
       </c>
       <c r="N207" s="1">
-        <v>5.5510000000000004E-3</v>
+        <v>0.005551</v>
       </c>
       <c r="O207" s="1">
         <v>81639</v>
       </c>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:15">
       <c r="A208" s="1" t="s">
         <v>220</v>
       </c>
@@ -9498,19 +10070,19 @@
         <v>51.25</v>
       </c>
       <c r="L208" s="1">
-        <v>9.4E-2</v>
+        <v>0.094</v>
       </c>
       <c r="M208" s="1">
-        <v>6.7000000000000004E-2</v>
+        <v>0.067</v>
       </c>
       <c r="N208" s="1">
-        <v>2.7179999999999999E-3</v>
+        <v>0.002718</v>
       </c>
       <c r="O208" s="1">
         <v>85429</v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:15">
       <c r="A209" s="1" t="s">
         <v>221</v>
       </c>
@@ -9536,19 +10108,19 @@
         <v>37.5</v>
       </c>
       <c r="L209" s="1">
-        <v>9.0999999999999998E-2</v>
+        <v>0.091</v>
       </c>
       <c r="M209" s="1">
-        <v>6.3E-2</v>
+        <v>0.063</v>
       </c>
       <c r="N209" s="1">
-        <v>2.0869999999999999E-3</v>
+        <v>0.002087</v>
       </c>
       <c r="O209" s="1">
         <v>86291</v>
       </c>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:15">
       <c r="A210" s="1" t="s">
         <v>222</v>
       </c>
@@ -9577,13 +10149,13 @@
         <v>0.106</v>
       </c>
       <c r="M210" s="1">
-        <v>7.0999999999999994E-2</v>
+        <v>0.071</v>
       </c>
       <c r="N210" s="1">
-        <v>2.4169999999999999E-3</v>
-      </c>
-    </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.002417</v>
+      </c>
+    </row>
+    <row r="211" spans="1:15">
       <c r="A211" s="1" t="s">
         <v>223</v>
       </c>
@@ -9609,19 +10181,19 @@
         <v>33.75</v>
       </c>
       <c r="L211" s="1">
-        <v>0.10299999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="M211" s="1">
-        <v>6.5000000000000002E-2</v>
+        <v>0.065</v>
       </c>
       <c r="N211" s="1">
-        <v>2.2899999999999999E-3</v>
+        <v>0.00229</v>
       </c>
       <c r="O211" s="1">
         <v>83897</v>
       </c>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:15">
       <c r="A212" s="1" t="s">
         <v>224</v>
       </c>
@@ -9647,16 +10219,16 @@
         <v>50</v>
       </c>
       <c r="L212" s="1">
-        <v>7.8E-2</v>
+        <v>0.078</v>
       </c>
       <c r="M212" s="1">
         <v>0.17</v>
       </c>
       <c r="N212" s="1">
-        <v>5.0280000000000004E-3</v>
-      </c>
-    </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.005028</v>
+      </c>
+    </row>
+    <row r="213" spans="1:15">
       <c r="A213" s="1" t="s">
         <v>225</v>
       </c>
@@ -9688,10 +10260,10 @@
         <v>0.108</v>
       </c>
       <c r="N213" s="1">
-        <v>5.4599999999999996E-3</v>
-      </c>
-    </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.00546</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15">
       <c r="A214" s="1" t="s">
         <v>226</v>
       </c>
@@ -9717,16 +10289,16 @@
         <v>50</v>
       </c>
       <c r="L214" s="1">
-        <v>8.2000000000000003E-2</v>
+        <v>0.082</v>
       </c>
       <c r="M214" s="1">
-        <v>8.2000000000000003E-2</v>
+        <v>0.082</v>
       </c>
       <c r="N214" s="1">
-        <v>3.1080000000000001E-3</v>
-      </c>
-    </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.003108</v>
+      </c>
+    </row>
+    <row r="215" spans="1:15">
       <c r="A215" s="1" t="s">
         <v>227</v>
       </c>
@@ -9752,16 +10324,16 @@
         <v>43.75</v>
       </c>
       <c r="L215" s="1">
-        <v>9.9000000000000005E-2</v>
+        <v>0.099</v>
       </c>
       <c r="M215" s="1">
         <v>0.08</v>
       </c>
       <c r="N215" s="1">
-        <v>2.9970000000000001E-3</v>
-      </c>
-    </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.002997</v>
+      </c>
+    </row>
+    <row r="216" spans="1:15">
       <c r="A216" s="1" t="s">
         <v>228</v>
       </c>
@@ -9784,19 +10356,19 @@
         <v>33.75</v>
       </c>
       <c r="L216" s="1">
-        <v>9.5000000000000001E-2</v>
+        <v>0.095</v>
       </c>
       <c r="M216" s="1">
-        <v>5.8999999999999997E-2</v>
+        <v>0.059</v>
       </c>
       <c r="N216" s="1">
-        <v>2.784E-3</v>
+        <v>0.002784</v>
       </c>
       <c r="O216" s="1">
         <v>83888</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:15">
       <c r="A217" s="1" t="s">
         <v>229</v>
       </c>
@@ -9822,16 +10394,16 @@
         <v>40</v>
       </c>
       <c r="L217" s="1">
-        <v>7.8E-2</v>
+        <v>0.078</v>
       </c>
       <c r="M217" s="1">
         <v>0.156</v>
       </c>
       <c r="N217" s="1">
-        <v>6.9300000000000004E-3</v>
-      </c>
-    </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.00693</v>
+      </c>
+    </row>
+    <row r="218" spans="1:15">
       <c r="A218" s="1" t="s">
         <v>230</v>
       </c>
@@ -9860,16 +10432,16 @@
         <v>0.08</v>
       </c>
       <c r="M218" s="1">
-        <v>9.6000000000000002E-2</v>
+        <v>0.096</v>
       </c>
       <c r="N218" s="1">
-        <v>4.2030000000000001E-3</v>
+        <v>0.004203</v>
       </c>
       <c r="O218" s="1">
         <v>82201</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:15">
       <c r="A219" s="1" t="s">
         <v>231</v>
       </c>
@@ -9895,19 +10467,19 @@
         <v>26.25</v>
       </c>
       <c r="L219" s="1">
-        <v>0.10299999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="M219" s="1">
-        <v>8.3000000000000004E-2</v>
+        <v>0.083</v>
       </c>
       <c r="N219" s="1">
-        <v>4.2719999999999998E-3</v>
+        <v>0.004272</v>
       </c>
       <c r="O219" s="1">
         <v>86969</v>
       </c>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:15">
       <c r="A220" s="1" t="s">
         <v>232</v>
       </c>
@@ -9933,19 +10505,19 @@
         <v>37.5</v>
       </c>
       <c r="L220" s="1">
-        <v>9.1999999999999998E-2</v>
+        <v>0.092</v>
       </c>
       <c r="M220" s="1">
-        <v>7.8E-2</v>
+        <v>0.078</v>
       </c>
       <c r="N220" s="1">
-        <v>2.9919999999999999E-3</v>
+        <v>0.002992</v>
       </c>
       <c r="O220" s="1">
         <v>83894</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:15">
       <c r="A221" s="1" t="s">
         <v>233</v>
       </c>
@@ -9971,19 +10543,19 @@
         <v>46.25</v>
       </c>
       <c r="L221" s="1">
-        <v>9.0999999999999998E-2</v>
+        <v>0.091</v>
       </c>
       <c r="M221" s="1">
-        <v>6.6000000000000003E-2</v>
+        <v>0.066</v>
       </c>
       <c r="N221" s="1">
-        <v>1.8710000000000001E-3</v>
+        <v>0.001871</v>
       </c>
       <c r="O221" s="1">
         <v>81601</v>
       </c>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:15">
       <c r="A222" s="1" t="s">
         <v>234</v>
       </c>
@@ -10006,19 +10578,19 @@
         <v>37.5</v>
       </c>
       <c r="L222" s="1">
-        <v>8.5000000000000006E-2</v>
+        <v>0.085</v>
       </c>
       <c r="M222" s="1">
-        <v>3.4000000000000002E-2</v>
+        <v>0.034</v>
       </c>
       <c r="N222" s="1">
-        <v>1.4239999999999999E-3</v>
+        <v>0.001424</v>
       </c>
       <c r="O222" s="1">
         <v>85415</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:15">
       <c r="A223" s="1" t="s">
         <v>235</v>
       </c>
@@ -10041,19 +10613,19 @@
         <v>35</v>
       </c>
       <c r="L223" s="1">
-        <v>8.8999999999999996E-2</v>
+        <v>0.089</v>
       </c>
       <c r="M223" s="1">
-        <v>0.19600000000000001</v>
+        <v>0.196</v>
       </c>
       <c r="N223" s="1">
-        <v>9.665E-3</v>
+        <v>0.009665</v>
       </c>
       <c r="O223" s="1">
         <v>85420</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:15">
       <c r="A224" s="1" t="s">
         <v>236</v>
       </c>
@@ -10079,19 +10651,19 @@
         <v>41.25</v>
       </c>
       <c r="L224" s="1">
-        <v>7.2999999999999995E-2</v>
+        <v>0.073</v>
       </c>
       <c r="M224" s="1">
         <v>0.111</v>
       </c>
       <c r="N224" s="1">
-        <v>4.7169999999999998E-3</v>
+        <v>0.004717</v>
       </c>
       <c r="O224" s="1">
         <v>85811</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:15">
       <c r="A225" s="1" t="s">
         <v>237</v>
       </c>
@@ -10117,19 +10689,19 @@
         <v>41.25</v>
       </c>
       <c r="L225" s="1">
-        <v>9.8000000000000004E-2</v>
+        <v>0.098</v>
       </c>
       <c r="M225" s="1">
         <v>0.104</v>
       </c>
       <c r="N225" s="1">
-        <v>2.9359999999999998E-3</v>
+        <v>0.002936</v>
       </c>
       <c r="O225" s="1">
         <v>87006</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:15">
       <c r="A226" s="1" t="s">
         <v>238</v>
       </c>
@@ -10155,19 +10727,19 @@
         <v>28.75</v>
       </c>
       <c r="L226" s="1">
-        <v>9.5000000000000001E-2</v>
+        <v>0.095</v>
       </c>
       <c r="M226" s="1">
-        <v>8.2000000000000003E-2</v>
+        <v>0.082</v>
       </c>
       <c r="N226" s="1">
-        <v>3.1259999999999999E-3</v>
+        <v>0.003126</v>
       </c>
       <c r="O226" s="1">
         <v>85815</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:15">
       <c r="A227" s="1" t="s">
         <v>239</v>
       </c>
@@ -10187,19 +10759,19 @@
         <v>31.25</v>
       </c>
       <c r="L227" s="1">
-        <v>9.6000000000000002E-2</v>
+        <v>0.096</v>
       </c>
       <c r="M227" s="1">
-        <v>8.2000000000000003E-2</v>
+        <v>0.082</v>
       </c>
       <c r="N227" s="1">
-        <v>2.7009999999999998E-3</v>
+        <v>0.002701</v>
       </c>
       <c r="O227" s="1">
         <v>83961</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:15">
       <c r="A228" s="1" t="s">
         <v>240</v>
       </c>
@@ -10225,19 +10797,19 @@
         <v>56.25</v>
       </c>
       <c r="L228" s="1">
-        <v>9.5000000000000001E-2</v>
+        <v>0.095</v>
       </c>
       <c r="M228" s="1">
-        <v>6.8000000000000005E-2</v>
+        <v>0.068</v>
       </c>
       <c r="N228" s="1">
-        <v>3.1310000000000001E-3</v>
+        <v>0.003131</v>
       </c>
       <c r="O228" s="1">
         <v>80516</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:15">
       <c r="A229" s="1" t="s">
         <v>241</v>
       </c>
@@ -10266,16 +10838,16 @@
         <v>0.107</v>
       </c>
       <c r="M229" s="1">
-        <v>5.6000000000000001E-2</v>
+        <v>0.056</v>
       </c>
       <c r="N229" s="1">
-        <v>2.0370000000000002E-3</v>
+        <v>0.002037</v>
       </c>
       <c r="O229" s="1">
         <v>85848</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:15">
       <c r="A230" s="1" t="s">
         <v>242</v>
       </c>
@@ -10301,19 +10873,19 @@
         <v>28.75</v>
       </c>
       <c r="L230" s="1">
-        <v>0.10199999999999999</v>
+        <v>0.102</v>
       </c>
       <c r="M230" s="1">
-        <v>5.3999999999999999E-2</v>
+        <v>0.054</v>
       </c>
       <c r="N230" s="1">
-        <v>2.2369999999999998E-3</v>
+        <v>0.002237</v>
       </c>
       <c r="O230" s="1">
         <v>83906</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:15">
       <c r="A231" s="1" t="s">
         <v>243</v>
       </c>
@@ -10339,19 +10911,19 @@
         <v>27.5</v>
       </c>
       <c r="L231" s="1">
-        <v>9.6000000000000002E-2</v>
+        <v>0.096</v>
       </c>
       <c r="M231" s="1">
-        <v>4.5999999999999999E-2</v>
+        <v>0.046</v>
       </c>
       <c r="N231" s="1">
-        <v>2.5010000000000002E-3</v>
+        <v>0.002501</v>
       </c>
       <c r="O231" s="1">
         <v>83976</v>
       </c>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:15">
       <c r="A232" s="1" t="s">
         <v>244</v>
       </c>
@@ -10380,16 +10952,16 @@
         <v>0.09</v>
       </c>
       <c r="M232" s="1">
-        <v>3.2000000000000001E-2</v>
+        <v>0.032</v>
       </c>
       <c r="N232" s="1">
-        <v>1.6609999999999999E-3</v>
+        <v>0.001661</v>
       </c>
       <c r="O232" s="1">
         <v>83964</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:15">
       <c r="A233" s="1" t="s">
         <v>245</v>
       </c>
@@ -10415,16 +10987,16 @@
         <v>37.5</v>
       </c>
       <c r="L233" s="1">
-        <v>9.7000000000000003E-2</v>
+        <v>0.097</v>
       </c>
       <c r="M233" s="1">
-        <v>0.29599999999999999</v>
+        <v>0.296</v>
       </c>
       <c r="N233" s="1">
-        <v>1.0617E-2</v>
-      </c>
-    </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.010617</v>
+      </c>
+    </row>
+    <row r="234" spans="1:15">
       <c r="A234" s="1" t="s">
         <v>246</v>
       </c>
@@ -10444,19 +11016,19 @@
         <v>33.75</v>
       </c>
       <c r="L234" s="1">
-        <v>5.8999999999999997E-2</v>
+        <v>0.059</v>
       </c>
       <c r="M234" s="1">
-        <v>6.5000000000000002E-2</v>
+        <v>0.065</v>
       </c>
       <c r="N234" s="1">
-        <v>3.862E-3</v>
+        <v>0.003862</v>
       </c>
       <c r="O234" s="1">
         <v>83936</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:15">
       <c r="A235" s="1" t="s">
         <v>247</v>
       </c>
@@ -10482,19 +11054,19 @@
         <v>32.5</v>
       </c>
       <c r="L235" s="1">
-        <v>9.4E-2</v>
+        <v>0.094</v>
       </c>
       <c r="M235" s="1">
         <v>0.04</v>
       </c>
       <c r="N235" s="1">
-        <v>1.689E-3</v>
+        <v>0.001689</v>
       </c>
       <c r="O235" s="1">
         <v>86300</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:15">
       <c r="A236" s="1" t="s">
         <v>248</v>
       </c>
@@ -10520,19 +11092,19 @@
         <v>46.25</v>
       </c>
       <c r="L236" s="1">
-        <v>8.5000000000000006E-2</v>
+        <v>0.085</v>
       </c>
       <c r="M236" s="1">
-        <v>5.8999999999999997E-2</v>
+        <v>0.059</v>
       </c>
       <c r="N236" s="1">
-        <v>2.6340000000000001E-3</v>
+        <v>0.002634</v>
       </c>
       <c r="O236" s="1">
         <v>81632</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:15">
       <c r="A237" s="1" t="s">
         <v>249</v>
       </c>
@@ -10558,19 +11130,19 @@
         <v>41.25</v>
       </c>
       <c r="L237" s="1">
-        <v>8.8999999999999996E-2</v>
+        <v>0.089</v>
       </c>
       <c r="M237" s="1">
-        <v>6.7000000000000004E-2</v>
+        <v>0.067</v>
       </c>
       <c r="N237" s="1">
-        <v>2.8349999999999998E-3</v>
+        <v>0.002835</v>
       </c>
       <c r="O237" s="1">
         <v>86396</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:15">
       <c r="A238" s="1" t="s">
         <v>250</v>
       </c>
@@ -10596,19 +11168,19 @@
         <v>47.5</v>
       </c>
       <c r="L238" s="1">
-        <v>0.10299999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="M238" s="1">
-        <v>6.6000000000000003E-2</v>
+        <v>0.066</v>
       </c>
       <c r="N238" s="1">
-        <v>2.7699999999999999E-3</v>
+        <v>0.00277</v>
       </c>
       <c r="O238" s="1">
         <v>85849</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:15">
       <c r="A239" s="1" t="s">
         <v>251</v>
       </c>
@@ -10631,16 +11203,16 @@
         <v>0.112</v>
       </c>
       <c r="M239" s="1">
-        <v>5.2999999999999999E-2</v>
+        <v>0.053</v>
       </c>
       <c r="N239" s="1">
-        <v>1.688E-3</v>
+        <v>0.001688</v>
       </c>
       <c r="O239" s="1">
         <v>85829</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:15">
       <c r="A240" s="1" t="s">
         <v>252</v>
       </c>
@@ -10666,16 +11238,16 @@
         <v>47.5</v>
       </c>
       <c r="L240" s="1">
-        <v>0.10100000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="M240" s="1">
         <v>0.123</v>
       </c>
       <c r="N240" s="1">
-        <v>4.0419999999999996E-3</v>
-      </c>
-    </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.004042</v>
+      </c>
+    </row>
+    <row r="241" spans="1:15">
       <c r="A241" s="1" t="s">
         <v>253</v>
       </c>
@@ -10701,16 +11273,16 @@
         <v>30</v>
       </c>
       <c r="L241" s="1">
-        <v>7.9000000000000001E-2</v>
+        <v>0.079</v>
       </c>
       <c r="M241" s="1">
         <v>0.129</v>
       </c>
       <c r="N241" s="1">
-        <v>5.411E-3</v>
-      </c>
-    </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.005411</v>
+      </c>
+    </row>
+    <row r="242" spans="1:15">
       <c r="A242" s="1" t="s">
         <v>254</v>
       </c>
@@ -10736,16 +11308,16 @@
         <v>0.108</v>
       </c>
       <c r="M242" s="1">
-        <v>0.56499999999999995</v>
+        <v>0.565</v>
       </c>
       <c r="N242" s="1">
-        <v>9.6609999999999994E-3</v>
+        <v>0.009661</v>
       </c>
       <c r="O242" s="1">
         <v>85399</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:15">
       <c r="A243" s="1" t="s">
         <v>255</v>
       </c>
@@ -10771,16 +11343,16 @@
         <v>26.25</v>
       </c>
       <c r="L243" s="1">
-        <v>7.6999999999999999E-2</v>
+        <v>0.077</v>
       </c>
       <c r="M243" s="1">
-        <v>0.16400000000000001</v>
+        <v>0.164</v>
       </c>
       <c r="N243" s="1">
-        <v>8.0079999999999995E-3</v>
-      </c>
-    </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.008008</v>
+      </c>
+    </row>
+    <row r="244" spans="1:15">
       <c r="A244" s="1" t="s">
         <v>256</v>
       </c>
@@ -10806,16 +11378,16 @@
         <v>31.25</v>
       </c>
       <c r="L244" s="1">
-        <v>9.1999999999999998E-2</v>
+        <v>0.092</v>
       </c>
       <c r="M244" s="1">
-        <v>7.8E-2</v>
+        <v>0.078</v>
       </c>
       <c r="N244" s="1">
-        <v>2.9750000000000002E-3</v>
-      </c>
-    </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.002975</v>
+      </c>
+    </row>
+    <row r="245" spans="1:15">
       <c r="A245" s="1" t="s">
         <v>257</v>
       </c>
@@ -10841,16 +11413,16 @@
         <v>0.105</v>
       </c>
       <c r="M245" s="1">
-        <v>6.7000000000000004E-2</v>
+        <v>0.067</v>
       </c>
       <c r="N245" s="1">
-        <v>2.663E-3</v>
+        <v>0.002663</v>
       </c>
       <c r="O245" s="1">
         <v>85424</v>
       </c>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:15">
       <c r="A246" s="1" t="s">
         <v>258</v>
       </c>
@@ -10876,19 +11448,19 @@
         <v>30</v>
       </c>
       <c r="L246" s="1">
-        <v>0.10299999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="M246" s="1">
-        <v>4.8000000000000001E-2</v>
+        <v>0.048</v>
       </c>
       <c r="N246" s="1">
-        <v>1.9480000000000001E-3</v>
+        <v>0.001948</v>
       </c>
       <c r="O246" s="1">
         <v>85808</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:15">
       <c r="A247" s="1" t="s">
         <v>259</v>
       </c>
@@ -10917,16 +11489,16 @@
         <v>0.1</v>
       </c>
       <c r="M247" s="1">
-        <v>6.6000000000000003E-2</v>
+        <v>0.066</v>
       </c>
       <c r="N247" s="1">
-        <v>2.2769999999999999E-3</v>
+        <v>0.002277</v>
       </c>
       <c r="O247" s="1">
         <v>86975</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:15">
       <c r="A248" s="1" t="s">
         <v>260</v>
       </c>
@@ -10949,19 +11521,19 @@
         <v>40</v>
       </c>
       <c r="L248" s="1">
-        <v>0.10299999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="M248" s="1">
-        <v>3.3000000000000002E-2</v>
+        <v>0.033</v>
       </c>
       <c r="N248" s="1">
-        <v>1.07E-3</v>
+        <v>0.00107</v>
       </c>
       <c r="O248" s="1">
         <v>85838</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:15">
       <c r="A249" s="1" t="s">
         <v>261</v>
       </c>
@@ -10990,16 +11562,16 @@
         <v>0.1</v>
       </c>
       <c r="M249" s="1">
-        <v>3.1E-2</v>
+        <v>0.031</v>
       </c>
       <c r="N249" s="1">
-        <v>1.364E-3</v>
+        <v>0.001364</v>
       </c>
       <c r="O249" s="1">
         <v>83895</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:15">
       <c r="A250" s="1" t="s">
         <v>262</v>
       </c>
@@ -11028,16 +11600,16 @@
         <v>0.105</v>
       </c>
       <c r="M250" s="1">
-        <v>6.6000000000000003E-2</v>
+        <v>0.066</v>
       </c>
       <c r="N250" s="1">
-        <v>2.3700000000000001E-3</v>
+        <v>0.00237</v>
       </c>
       <c r="O250" s="1">
         <v>82194</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:15">
       <c r="A251" s="1" t="s">
         <v>263</v>
       </c>
@@ -11063,19 +11635,19 @@
         <v>33.75</v>
       </c>
       <c r="L251" s="1">
-        <v>0.10100000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="M251" s="1">
-        <v>0.10100000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="N251" s="1">
-        <v>2.81E-3</v>
+        <v>0.00281</v>
       </c>
       <c r="O251" s="1">
         <v>85800</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:15">
       <c r="A252" s="1" t="s">
         <v>264</v>
       </c>
@@ -11101,19 +11673,19 @@
         <v>30</v>
       </c>
       <c r="L252" s="1">
-        <v>9.4E-2</v>
+        <v>0.094</v>
       </c>
       <c r="M252" s="1">
-        <v>7.6999999999999999E-2</v>
+        <v>0.077</v>
       </c>
       <c r="N252" s="1">
-        <v>3.4949999999999998E-3</v>
+        <v>0.003495</v>
       </c>
       <c r="O252" s="1">
         <v>80540</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:15">
       <c r="A253" s="1" t="s">
         <v>265</v>
       </c>
@@ -11136,19 +11708,19 @@
         <v>36.25</v>
       </c>
       <c r="L253" s="1">
-        <v>9.9000000000000005E-2</v>
+        <v>0.099</v>
       </c>
       <c r="M253" s="1">
-        <v>5.1999999999999998E-2</v>
+        <v>0.052</v>
       </c>
       <c r="N253" s="1">
-        <v>2.1329999999999999E-3</v>
+        <v>0.002133</v>
       </c>
       <c r="O253" s="1">
         <v>85418</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:15">
       <c r="A254" s="1" t="s">
         <v>266</v>
       </c>
@@ -11174,19 +11746,19 @@
         <v>33.75</v>
       </c>
       <c r="L254" s="1">
-        <v>9.4E-2</v>
+        <v>0.094</v>
       </c>
       <c r="M254" s="1">
         <v>0.121</v>
       </c>
       <c r="N254" s="1">
-        <v>3.5360000000000001E-3</v>
+        <v>0.003536</v>
       </c>
       <c r="O254" s="1">
         <v>84409</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:15">
       <c r="A255" s="1" t="s">
         <v>267</v>
       </c>
@@ -11212,19 +11784,19 @@
         <v>37.5</v>
       </c>
       <c r="L255" s="1">
-        <v>9.0999999999999998E-2</v>
+        <v>0.091</v>
       </c>
       <c r="M255" s="1">
-        <v>8.3000000000000004E-2</v>
+        <v>0.083</v>
       </c>
       <c r="N255" s="1">
-        <v>3.4129999999999998E-3</v>
+        <v>0.003413</v>
       </c>
       <c r="O255" s="1">
         <v>85861</v>
       </c>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:15">
       <c r="A256" s="1" t="s">
         <v>268</v>
       </c>
@@ -11244,19 +11816,19 @@
         <v>36.25</v>
       </c>
       <c r="L256" s="1">
-        <v>9.5000000000000001E-2</v>
+        <v>0.095</v>
       </c>
       <c r="M256" s="1">
-        <v>6.0999999999999999E-2</v>
+        <v>0.061</v>
       </c>
       <c r="N256" s="1">
-        <v>2.5249999999999999E-3</v>
+        <v>0.002525</v>
       </c>
       <c r="O256" s="1">
         <v>83941</v>
       </c>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:15">
       <c r="A257" s="1" t="s">
         <v>269</v>
       </c>
@@ -11282,19 +11854,19 @@
         <v>48.75</v>
       </c>
       <c r="L257" s="1">
-        <v>9.9000000000000005E-2</v>
+        <v>0.099</v>
       </c>
       <c r="M257" s="1">
-        <v>3.4000000000000002E-2</v>
+        <v>0.034</v>
       </c>
       <c r="N257" s="1">
-        <v>1.6429999999999999E-3</v>
+        <v>0.001643</v>
       </c>
       <c r="O257" s="1">
         <v>82166</v>
       </c>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:15">
       <c r="A258" s="1" t="s">
         <v>270</v>
       </c>
@@ -11320,16 +11892,16 @@
         <v>46.25</v>
       </c>
       <c r="L258" s="1">
-        <v>0.10199999999999999</v>
+        <v>0.102</v>
       </c>
       <c r="M258" s="1">
         <v>0.109</v>
       </c>
       <c r="N258" s="1">
-        <v>3.702E-3</v>
-      </c>
-    </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.003702</v>
+      </c>
+    </row>
+    <row r="259" spans="1:15">
       <c r="A259" s="1" t="s">
         <v>271</v>
       </c>
@@ -11340,16 +11912,16 @@
         <v>1</v>
       </c>
       <c r="L259" s="1">
-        <v>8.7999999999999995E-2</v>
+        <v>0.088</v>
       </c>
       <c r="M259" s="1">
         <v>0.223</v>
       </c>
       <c r="N259" s="1">
-        <v>7.6080000000000002E-3</v>
-      </c>
-    </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.007608</v>
+      </c>
+    </row>
+    <row r="260" spans="1:15">
       <c r="A260" s="1" t="s">
         <v>272</v>
       </c>
@@ -11360,19 +11932,19 @@
         <v>2</v>
       </c>
       <c r="L260" s="1">
-        <v>8.5000000000000006E-2</v>
+        <v>0.085</v>
       </c>
       <c r="M260" s="1">
-        <v>0.13100000000000001</v>
+        <v>0.131</v>
       </c>
       <c r="N260" s="1">
-        <v>4.7710000000000001E-3</v>
+        <v>0.004771</v>
       </c>
       <c r="O260" s="1">
         <v>79990</v>
       </c>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:15">
       <c r="A261" s="1" t="s">
         <v>273</v>
       </c>
@@ -11383,19 +11955,19 @@
         <v>1</v>
       </c>
       <c r="L261" s="1">
-        <v>8.6999999999999994E-2</v>
+        <v>0.087</v>
       </c>
       <c r="M261" s="1">
-        <v>0.10100000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="N261" s="1">
-        <v>2.869E-3</v>
+        <v>0.002869</v>
       </c>
       <c r="O261" s="1">
         <v>85351</v>
       </c>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:15">
       <c r="A262" s="1" t="s">
         <v>274</v>
       </c>
@@ -11406,16 +11978,16 @@
         <v>2</v>
       </c>
       <c r="L262" s="1">
-        <v>9.0999999999999998E-2</v>
+        <v>0.091</v>
       </c>
       <c r="M262" s="1">
-        <v>9.9000000000000005E-2</v>
+        <v>0.099</v>
       </c>
       <c r="N262" s="1">
-        <v>4.1859999999999996E-3</v>
-      </c>
-    </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.004186</v>
+      </c>
+    </row>
+    <row r="263" spans="1:15">
       <c r="A263" s="1" t="s">
         <v>275</v>
       </c>
@@ -11426,19 +11998,19 @@
         <v>2</v>
       </c>
       <c r="L263" s="1">
-        <v>8.4000000000000005E-2</v>
+        <v>0.084</v>
       </c>
       <c r="M263" s="1">
-        <v>9.6000000000000002E-2</v>
+        <v>0.096</v>
       </c>
       <c r="N263" s="1">
-        <v>3.738E-3</v>
+        <v>0.003738</v>
       </c>
       <c r="O263" s="1">
         <v>79982</v>
       </c>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:15">
       <c r="A264" s="1" t="s">
         <v>276</v>
       </c>
@@ -11449,16 +12021,16 @@
         <v>1</v>
       </c>
       <c r="L264" s="1">
-        <v>9.1999999999999998E-2</v>
+        <v>0.092</v>
       </c>
       <c r="M264" s="1">
-        <v>9.0999999999999998E-2</v>
+        <v>0.091</v>
       </c>
       <c r="N264" s="1">
-        <v>3.8270000000000001E-3</v>
-      </c>
-    </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.003827</v>
+      </c>
+    </row>
+    <row r="265" spans="1:15">
       <c r="A265" s="1" t="s">
         <v>277</v>
       </c>
@@ -11469,19 +12041,19 @@
         <v>2</v>
       </c>
       <c r="L265" s="1">
-        <v>9.9000000000000005E-2</v>
+        <v>0.099</v>
       </c>
       <c r="M265" s="1">
         <v>0.08</v>
       </c>
       <c r="N265" s="1">
-        <v>2.2829999999999999E-3</v>
+        <v>0.002283</v>
       </c>
       <c r="O265" s="1">
         <v>79981</v>
       </c>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:15">
       <c r="A266" s="1" t="s">
         <v>278</v>
       </c>
@@ -11492,16 +12064,16 @@
         <v>1</v>
       </c>
       <c r="L266" s="1">
-        <v>0.10100000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="M266" s="1">
-        <v>6.9000000000000006E-2</v>
+        <v>0.069</v>
       </c>
       <c r="N266" s="1">
-        <v>3.3430000000000001E-3</v>
-      </c>
-    </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.003343</v>
+      </c>
+    </row>
+    <row r="267" spans="1:15">
       <c r="A267" s="1" t="s">
         <v>279</v>
       </c>
@@ -11515,16 +12087,16 @@
         <v>0.114</v>
       </c>
       <c r="M267" s="1">
-        <v>6.2E-2</v>
+        <v>0.062</v>
       </c>
       <c r="N267" s="1">
-        <v>2.532E-3</v>
+        <v>0.002532</v>
       </c>
       <c r="O267" s="1">
         <v>80508</v>
       </c>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:15">
       <c r="A268" s="1" t="s">
         <v>280</v>
       </c>
@@ -11535,16 +12107,16 @@
         <v>1</v>
       </c>
       <c r="L268" s="1">
-        <v>9.1999999999999998E-2</v>
+        <v>0.092</v>
       </c>
       <c r="M268" s="1">
-        <v>6.2E-2</v>
+        <v>0.062</v>
       </c>
       <c r="N268" s="1">
-        <v>2.3140000000000001E-3</v>
-      </c>
-    </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.002314</v>
+      </c>
+    </row>
+    <row r="269" spans="1:15">
       <c r="A269" s="1" t="s">
         <v>281</v>
       </c>
@@ -11558,16 +12130,16 @@
         <v>0.111</v>
       </c>
       <c r="M269" s="1">
-        <v>6.0999999999999999E-2</v>
+        <v>0.061</v>
       </c>
       <c r="N269" s="1">
-        <v>2.2799999999999999E-3</v>
+        <v>0.00228</v>
       </c>
       <c r="O269" s="1">
         <v>86378</v>
       </c>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:15">
       <c r="A270" s="1" t="s">
         <v>282</v>
       </c>
@@ -11581,16 +12153,16 @@
         <v>0.112</v>
       </c>
       <c r="M270" s="1">
-        <v>6.0999999999999999E-2</v>
+        <v>0.061</v>
       </c>
       <c r="N270" s="1">
-        <v>2.1970000000000002E-3</v>
+        <v>0.002197</v>
       </c>
       <c r="O270" s="1">
         <v>80507</v>
       </c>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:15">
       <c r="A271" s="1" t="s">
         <v>283</v>
       </c>
@@ -11601,19 +12173,19 @@
         <v>2</v>
       </c>
       <c r="L271" s="1">
-        <v>9.6000000000000002E-2</v>
+        <v>0.096</v>
       </c>
       <c r="M271" s="1">
-        <v>6.0999999999999999E-2</v>
+        <v>0.061</v>
       </c>
       <c r="N271" s="1">
-        <v>2.032E-3</v>
+        <v>0.002032</v>
       </c>
       <c r="O271" s="1">
         <v>79983</v>
       </c>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:15">
       <c r="A272" s="1" t="s">
         <v>284</v>
       </c>
@@ -11627,13 +12199,13 @@
         <v>0.106</v>
       </c>
       <c r="M272" s="1">
-        <v>5.1999999999999998E-2</v>
+        <v>0.052</v>
       </c>
       <c r="N272" s="1">
-        <v>2.0230000000000001E-3</v>
-      </c>
-    </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.002023</v>
+      </c>
+    </row>
+    <row r="273" spans="1:15">
       <c r="A273" s="1" t="s">
         <v>285</v>
       </c>
@@ -11644,19 +12216,19 @@
         <v>2</v>
       </c>
       <c r="L273" s="1">
-        <v>9.7000000000000003E-2</v>
+        <v>0.097</v>
       </c>
       <c r="M273" s="1">
-        <v>4.9000000000000002E-2</v>
+        <v>0.049</v>
       </c>
       <c r="N273" s="1">
-        <v>2.0249999999999999E-3</v>
+        <v>0.002025</v>
       </c>
       <c r="O273" s="1">
         <v>81605</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:15">
       <c r="A274" s="1" t="s">
         <v>286</v>
       </c>
@@ -11670,13 +12242,13 @@
         <v>0.104</v>
       </c>
       <c r="M274" s="1">
-        <v>4.2999999999999997E-2</v>
+        <v>0.043</v>
       </c>
       <c r="N274" s="1">
-        <v>1.769E-3</v>
-      </c>
-    </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.001769</v>
+      </c>
+    </row>
+    <row r="275" spans="1:15">
       <c r="A275" s="1" t="s">
         <v>287</v>
       </c>
@@ -11705,16 +12277,16 @@
         <v>26</v>
       </c>
       <c r="L275" s="1">
-        <v>6.8111258999999993E-2</v>
+        <v>0.068111259</v>
       </c>
       <c r="M275" s="1">
         <v>0.308</v>
       </c>
       <c r="N275" s="1">
-        <v>1.4325581E-2</v>
-      </c>
-    </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.014325581</v>
+      </c>
+    </row>
+    <row r="276" spans="1:15">
       <c r="A276" s="1" t="s">
         <v>288</v>
       </c>
@@ -11743,19 +12315,19 @@
         <v>20</v>
       </c>
       <c r="L276" s="1">
-        <v>6.9550788000000002E-2</v>
+        <v>0.069550788</v>
       </c>
       <c r="M276" s="1">
-        <v>0.78600000000000003</v>
+        <v>0.786</v>
       </c>
       <c r="N276" s="1">
-        <v>3.2900794999999997E-2</v>
+        <v>0.032900795</v>
       </c>
       <c r="O276" s="1">
         <v>131596</v>
       </c>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:15">
       <c r="A277" s="1" t="s">
         <v>289</v>
       </c>
@@ -11784,19 +12356,19 @@
         <v>29</v>
       </c>
       <c r="L277" s="1">
-        <v>6.7649461999999994E-2</v>
+        <v>0.067649462</v>
       </c>
       <c r="M277" s="1">
         <v>0.505</v>
       </c>
       <c r="N277" s="1">
-        <v>2.5415198999999999E-2</v>
+        <v>0.025415199</v>
       </c>
       <c r="O277" s="1">
         <v>131616</v>
       </c>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:15">
       <c r="A278" s="1" t="s">
         <v>290</v>
       </c>
@@ -11825,19 +12397,19 @@
         <v>22</v>
       </c>
       <c r="L278" s="1">
-        <v>6.8909197000000005E-2</v>
+        <v>0.068909197</v>
       </c>
       <c r="M278" s="1">
-        <v>0.34499999999999997</v>
+        <v>0.345</v>
       </c>
       <c r="N278" s="1">
-        <v>1.9469526000000001E-2</v>
+        <v>0.019469526</v>
       </c>
       <c r="O278" s="1">
         <v>131643</v>
       </c>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:15">
       <c r="A279" s="1" t="s">
         <v>291</v>
       </c>
@@ -11866,19 +12438,19 @@
         <v>29</v>
       </c>
       <c r="L279" s="1">
-        <v>9.4582184999999999E-2</v>
+        <v>0.094582185</v>
       </c>
       <c r="M279" s="1">
         <v>0.126</v>
       </c>
       <c r="N279" s="1">
-        <v>4.7050039999999996E-3</v>
+        <v>0.004705004</v>
       </c>
       <c r="O279" s="1">
         <v>131640</v>
       </c>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:15">
       <c r="A280" s="1" t="s">
         <v>292</v>
       </c>
@@ -11907,19 +12479,19 @@
         <v>26</v>
       </c>
       <c r="L280" s="1">
-        <v>7.3442174999999998E-2</v>
+        <v>0.073442175</v>
       </c>
       <c r="M280" s="1">
-        <v>0.33500000000000002</v>
+        <v>0.335</v>
       </c>
       <c r="N280" s="1">
-        <v>1.1972838E-2</v>
+        <v>0.011972838</v>
       </c>
       <c r="O280" s="1">
         <v>131620</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:15">
       <c r="A281" s="1" t="s">
         <v>293</v>
       </c>
@@ -11948,19 +12520,19 @@
         <v>20</v>
       </c>
       <c r="L281" s="1">
-        <v>6.9971587000000002E-2</v>
+        <v>0.069971587</v>
       </c>
       <c r="M281" s="1">
-        <v>0.73199999999999998</v>
+        <v>0.732</v>
       </c>
       <c r="N281" s="1">
-        <v>4.4363635999999998E-2</v>
+        <v>0.044363636</v>
       </c>
       <c r="O281" s="1">
         <v>131666</v>
       </c>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:15">
       <c r="A282" s="1" t="s">
         <v>294</v>
       </c>
@@ -11989,19 +12561,19 @@
         <v>40</v>
       </c>
       <c r="L282" s="1">
-        <v>9.6489369000000005E-2</v>
+        <v>0.096489369</v>
       </c>
       <c r="M282" s="1">
-        <v>6.0999999999999999E-2</v>
+        <v>0.061</v>
       </c>
       <c r="N282" s="1">
-        <v>2.232796E-3</v>
+        <v>0.002232796</v>
       </c>
       <c r="O282" s="1">
         <v>131669</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:15">
       <c r="A283" s="1" t="s">
         <v>295</v>
       </c>
@@ -12030,19 +12602,19 @@
         <v>34</v>
       </c>
       <c r="L283" s="1">
-        <v>8.8046978999999997E-2</v>
+        <v>0.088046979</v>
       </c>
       <c r="M283" s="1">
-        <v>0.11799999999999999</v>
+        <v>0.118</v>
       </c>
       <c r="N283" s="1">
-        <v>5.077453E-3</v>
+        <v>0.005077453</v>
       </c>
       <c r="O283" s="1">
         <v>131599</v>
       </c>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:15">
       <c r="A284" s="1" t="s">
         <v>296</v>
       </c>
@@ -12071,19 +12643,19 @@
         <v>30</v>
       </c>
       <c r="L284" s="1">
-        <v>8.3543839999999994E-2</v>
+        <v>0.08354384</v>
       </c>
       <c r="M284" s="1">
-        <v>0.34499999999999997</v>
+        <v>0.345</v>
       </c>
       <c r="N284" s="1">
-        <v>1.5118316999999999E-2</v>
+        <v>0.015118317</v>
       </c>
       <c r="O284" s="1">
         <v>131624</v>
       </c>
     </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:15">
       <c r="A285" s="1" t="s">
         <v>297</v>
       </c>
@@ -12094,16 +12666,16 @@
         <v>2</v>
       </c>
       <c r="L285" s="1">
-        <v>9.8425382000000006E-2</v>
+        <v>0.098425382</v>
       </c>
       <c r="M285" s="1">
         <v>0.04</v>
       </c>
       <c r="N285" s="1">
-        <v>1.91022E-3</v>
-      </c>
-    </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.00191022</v>
+      </c>
+    </row>
+    <row r="286" spans="1:15">
       <c r="A286" s="1" t="s">
         <v>298</v>
       </c>
@@ -12114,16 +12686,16 @@
         <v>2</v>
       </c>
       <c r="L286" s="1">
-        <v>8.9541600999999998E-2</v>
+        <v>0.089541601</v>
       </c>
       <c r="M286" s="1">
-        <v>6.7000000000000004E-2</v>
+        <v>0.067</v>
       </c>
       <c r="N286" s="1">
-        <v>2.8068709999999998E-3</v>
-      </c>
-    </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.002806871</v>
+      </c>
+    </row>
+    <row r="287" spans="1:15">
       <c r="A287" s="1" t="s">
         <v>299</v>
       </c>
@@ -12134,16 +12706,16 @@
         <v>2</v>
       </c>
       <c r="L287" s="1">
-        <v>6.8808997999999996E-2</v>
+        <v>0.068808998</v>
       </c>
       <c r="M287" s="1">
         <v>0.157</v>
       </c>
       <c r="N287" s="1">
-        <v>9.1652069999999999E-3</v>
-      </c>
-    </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.009165207</v>
+      </c>
+    </row>
+    <row r="288" spans="1:15">
       <c r="A288" s="1" t="s">
         <v>300</v>
       </c>
@@ -12172,19 +12744,19 @@
         <v>28</v>
       </c>
       <c r="L288" s="1">
-        <v>6.8634433999999994E-2</v>
+        <v>0.068634434</v>
       </c>
       <c r="M288" s="1">
-        <v>0.17699999999999999</v>
+        <v>0.177</v>
       </c>
       <c r="N288" s="1">
-        <v>7.347447E-3</v>
+        <v>0.007347447</v>
       </c>
       <c r="O288" s="1">
         <v>131626</v>
       </c>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:15">
       <c r="A289" s="1" t="s">
         <v>301</v>
       </c>
@@ -12213,16 +12785,16 @@
         <v>40</v>
       </c>
       <c r="L289" s="1">
-        <v>7.4438398000000003E-2</v>
+        <v>0.074438398</v>
       </c>
       <c r="M289" s="1">
-        <v>9.7000000000000003E-2</v>
+        <v>0.097</v>
       </c>
       <c r="N289" s="1">
-        <v>4.5454550000000003E-3</v>
-      </c>
-    </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.004545455</v>
+      </c>
+    </row>
+    <row r="290" spans="1:15">
       <c r="A290" s="1" t="s">
         <v>302</v>
       </c>
@@ -12251,19 +12823,19 @@
         <v>35</v>
       </c>
       <c r="L290" s="1">
-        <v>7.6443858000000003E-2</v>
+        <v>0.076443858</v>
       </c>
       <c r="M290" s="1">
-        <v>0.29599999999999999</v>
+        <v>0.296</v>
       </c>
       <c r="N290" s="1">
-        <v>1.4189837E-2</v>
+        <v>0.014189837</v>
       </c>
       <c r="O290" s="1">
         <v>131672</v>
       </c>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:15">
       <c r="A291" s="1" t="s">
         <v>303</v>
       </c>
@@ -12292,19 +12864,19 @@
         <v>24</v>
       </c>
       <c r="L291" s="1">
-        <v>7.3498541000000001E-2</v>
+        <v>0.073498541</v>
       </c>
       <c r="M291" s="1">
         <v>0.25</v>
       </c>
       <c r="N291" s="1">
-        <v>8.7077669999999999E-3</v>
+        <v>0.008707767</v>
       </c>
       <c r="O291" s="1">
         <v>131651</v>
       </c>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:15">
       <c r="A292" s="1" t="s">
         <v>304</v>
       </c>
@@ -12333,19 +12905,19 @@
         <v>24</v>
       </c>
       <c r="L292" s="1">
-        <v>6.4416837000000005E-2</v>
+        <v>0.064416837</v>
       </c>
       <c r="M292" s="1">
-        <v>0.27100000000000002</v>
+        <v>0.271</v>
       </c>
       <c r="N292" s="1">
-        <v>1.5601612000000001E-2</v>
+        <v>0.015601612</v>
       </c>
       <c r="O292" s="1">
         <v>131623</v>
       </c>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:15">
       <c r="A293" s="1" t="s">
         <v>305</v>
       </c>
@@ -12374,19 +12946,19 @@
         <v>37</v>
       </c>
       <c r="L293" s="1">
-        <v>7.5697211E-2</v>
+        <v>0.075697211</v>
       </c>
       <c r="M293" s="1">
-        <v>1.7969999999999999</v>
+        <v>1.797</v>
       </c>
       <c r="N293" s="1">
-        <v>0.11972018700000001</v>
+        <v>0.119720187</v>
       </c>
       <c r="O293" s="1">
         <v>131633</v>
       </c>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:15">
       <c r="A294" s="1" t="s">
         <v>306</v>
       </c>
@@ -12415,19 +12987,19 @@
         <v>25</v>
       </c>
       <c r="L294" s="1">
-        <v>7.2132667999999997E-2</v>
+        <v>0.072132668</v>
       </c>
       <c r="M294" s="1">
-        <v>0.11899999999999999</v>
+        <v>0.119</v>
       </c>
       <c r="N294" s="1">
-        <v>6.3772780000000001E-3</v>
+        <v>0.006377278</v>
       </c>
       <c r="O294" s="1">
         <v>131597</v>
       </c>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:15">
       <c r="A295" s="1" t="s">
         <v>307</v>
       </c>
@@ -12456,19 +13028,19 @@
         <v>23</v>
       </c>
       <c r="L295" s="1">
-        <v>6.9178461999999996E-2</v>
+        <v>0.069178462</v>
       </c>
       <c r="M295" s="1">
-        <v>0.24099999999999999</v>
+        <v>0.241</v>
       </c>
       <c r="N295" s="1">
-        <v>1.2086259E-2</v>
+        <v>0.012086259</v>
       </c>
       <c r="O295" s="1">
         <v>131689</v>
       </c>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:15">
       <c r="A296" s="1" t="s">
         <v>308</v>
       </c>
@@ -12497,19 +13069,19 @@
         <v>28</v>
       </c>
       <c r="L296" s="1">
-        <v>6.0799236E-2</v>
+        <v>0.060799236</v>
       </c>
       <c r="M296" s="1">
         <v>0.157</v>
       </c>
       <c r="N296" s="1">
-        <v>7.2517320000000003E-3</v>
+        <v>0.007251732</v>
       </c>
       <c r="O296" s="1">
         <v>131607</v>
       </c>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:15">
       <c r="A297" s="1" t="s">
         <v>309</v>
       </c>
@@ -12538,19 +13110,19 @@
         <v>22</v>
       </c>
       <c r="L297" s="1">
-        <v>7.9988346000000002E-2</v>
+        <v>0.079988346</v>
       </c>
       <c r="M297" s="1">
-        <v>8.5999999999999993E-2</v>
+        <v>0.086</v>
       </c>
       <c r="N297" s="1">
-        <v>3.4803719999999998E-3</v>
+        <v>0.003480372</v>
       </c>
       <c r="O297" s="1">
         <v>131589</v>
       </c>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:15">
       <c r="A298" s="1" t="s">
         <v>310</v>
       </c>
@@ -12579,19 +13151,19 @@
         <v>36</v>
       </c>
       <c r="L298" s="1">
-        <v>9.0716742000000003E-2</v>
+        <v>0.090716742</v>
       </c>
       <c r="M298" s="1">
-        <v>6.8000000000000005E-2</v>
+        <v>0.068</v>
       </c>
       <c r="N298" s="1">
-        <v>3.304179E-3</v>
+        <v>0.003304179</v>
       </c>
       <c r="O298" s="1">
         <v>131674</v>
       </c>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:15">
       <c r="A299" s="1" t="s">
         <v>311</v>
       </c>
@@ -12620,19 +13192,19 @@
         <v>31</v>
       </c>
       <c r="L299" s="1">
-        <v>5.7757550999999997E-2</v>
+        <v>0.057757551</v>
       </c>
       <c r="M299" s="1">
-        <v>1.0980000000000001</v>
+        <v>1.098</v>
       </c>
       <c r="N299" s="1">
-        <v>7.8653294999999998E-2</v>
+        <v>0.078653295</v>
       </c>
       <c r="O299" s="1">
         <v>131687</v>
       </c>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:15">
       <c r="A300" s="1" t="s">
         <v>312</v>
       </c>
@@ -12661,19 +13233,19 @@
         <v>22</v>
       </c>
       <c r="L300" s="1">
-        <v>9.8559741000000006E-2</v>
+        <v>0.098559741</v>
       </c>
       <c r="M300" s="1">
         <v>0.03</v>
       </c>
       <c r="N300" s="1">
-        <v>1.2970169999999999E-3</v>
+        <v>0.001297017</v>
       </c>
       <c r="O300" s="1">
         <v>131724</v>
       </c>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:15">
       <c r="A301" s="1" t="s">
         <v>313</v>
       </c>
@@ -12702,19 +13274,19 @@
         <v>26</v>
       </c>
       <c r="L301" s="1">
-        <v>6.8936224000000004E-2</v>
+        <v>0.068936224</v>
       </c>
       <c r="M301" s="1">
-        <v>6.6000000000000003E-2</v>
+        <v>0.066</v>
       </c>
       <c r="N301" s="1">
-        <v>3.0123229999999999E-3</v>
+        <v>0.003012323</v>
       </c>
       <c r="O301" s="1">
         <v>131707</v>
       </c>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:15">
       <c r="A302" s="1" t="s">
         <v>314</v>
       </c>
@@ -12743,19 +13315,19 @@
         <v>31</v>
       </c>
       <c r="L302" s="1">
-        <v>8.7376842999999996E-2</v>
+        <v>0.087376843</v>
       </c>
       <c r="M302" s="1">
         <v>0.125</v>
       </c>
       <c r="N302" s="1">
-        <v>5.2988549999999999E-3</v>
+        <v>0.005298855</v>
       </c>
       <c r="O302" s="1">
         <v>131729</v>
       </c>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:15">
       <c r="A303" s="1" t="s">
         <v>315</v>
       </c>
@@ -12784,19 +13356,19 @@
         <v>21</v>
       </c>
       <c r="L303" s="1">
-        <v>9.2756785999999994E-2</v>
+        <v>0.092756786</v>
       </c>
       <c r="M303" s="1">
-        <v>4.7E-2</v>
+        <v>0.047</v>
       </c>
       <c r="N303" s="1">
-        <v>2.3039219999999999E-3</v>
+        <v>0.002303922</v>
       </c>
       <c r="O303" s="1">
         <v>131679</v>
       </c>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:15">
       <c r="A304" s="1" t="s">
         <v>316</v>
       </c>
@@ -12825,19 +13397,19 @@
         <v>27</v>
       </c>
       <c r="L304" s="1">
-        <v>9.0851807000000007E-2</v>
+        <v>0.090851807</v>
       </c>
       <c r="M304" s="1">
-        <v>6.0999999999999999E-2</v>
+        <v>0.061</v>
       </c>
       <c r="N304" s="1">
-        <v>1.923077E-3</v>
+        <v>0.001923077</v>
       </c>
       <c r="O304" s="1">
         <v>131710</v>
       </c>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:15">
       <c r="A305" s="1" t="s">
         <v>317</v>
       </c>
@@ -12866,19 +13438,19 @@
         <v>27</v>
       </c>
       <c r="L305" s="1">
-        <v>8.8115024E-2</v>
+        <v>0.088115024</v>
       </c>
       <c r="M305" s="1">
-        <v>5.8999999999999997E-2</v>
+        <v>0.059</v>
       </c>
       <c r="N305" s="1">
-        <v>2.944112E-3</v>
+        <v>0.002944112</v>
       </c>
       <c r="O305" s="1">
         <v>131711</v>
       </c>
     </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:15">
       <c r="A306" s="1" t="s">
         <v>318</v>
       </c>
@@ -12913,13 +13485,13 @@
         <v>0.04</v>
       </c>
       <c r="N306" s="1">
-        <v>1.3360049999999999E-3</v>
+        <v>0.001336005</v>
       </c>
       <c r="O306" s="1">
         <v>131700</v>
       </c>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:15">
       <c r="A307" s="1" t="s">
         <v>319</v>
       </c>
@@ -12948,19 +13520,19 @@
         <v>26</v>
       </c>
       <c r="L307" s="1">
-        <v>8.4211236999999994E-2</v>
+        <v>0.084211237</v>
       </c>
       <c r="M307" s="1">
-        <v>5.5E-2</v>
+        <v>0.055</v>
       </c>
       <c r="N307" s="1">
-        <v>2.2052930000000001E-3</v>
+        <v>0.002205293</v>
       </c>
       <c r="O307" s="1">
         <v>131723</v>
       </c>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:15">
       <c r="A308" s="1" t="s">
         <v>320</v>
       </c>
@@ -12989,19 +13561,19 @@
         <v>29</v>
       </c>
       <c r="L308" s="1">
-        <v>8.3622661000000001E-2</v>
+        <v>0.083622661</v>
       </c>
       <c r="M308" s="1">
         <v>0.108</v>
       </c>
       <c r="N308" s="1">
-        <v>5.4683539999999999E-3</v>
+        <v>0.005468354</v>
       </c>
       <c r="O308" s="1">
         <v>131663</v>
       </c>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:15">
       <c r="A309" s="1" t="s">
         <v>321</v>
       </c>
@@ -13030,19 +13602,19 @@
         <v>20</v>
       </c>
       <c r="L309" s="1">
-        <v>7.4300560000000002E-2</v>
+        <v>0.07430056</v>
       </c>
       <c r="M309" s="1">
         <v>0.106</v>
       </c>
       <c r="N309" s="1">
-        <v>5.7019899999999997E-3</v>
+        <v>0.00570199</v>
       </c>
       <c r="O309" s="1">
         <v>131690</v>
       </c>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:15">
       <c r="A310" s="1" t="s">
         <v>322</v>
       </c>
@@ -13071,19 +13643,19 @@
         <v>24</v>
       </c>
       <c r="L310" s="1">
-        <v>8.7210346999999994E-2</v>
+        <v>0.087210347</v>
       </c>
       <c r="M310" s="1">
-        <v>0.10100000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="N310" s="1">
-        <v>3.467216E-3</v>
+        <v>0.003467216</v>
       </c>
       <c r="O310" s="1">
         <v>131692</v>
       </c>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:15">
       <c r="A311" s="1" t="s">
         <v>323</v>
       </c>
@@ -13112,19 +13684,19 @@
         <v>35</v>
       </c>
       <c r="L311" s="1">
-        <v>8.0313958000000005E-2</v>
+        <v>0.080313958</v>
       </c>
       <c r="M311" s="1">
-        <v>5.6000000000000001E-2</v>
+        <v>0.056</v>
       </c>
       <c r="N311" s="1">
-        <v>2.9582670000000001E-3</v>
+        <v>0.002958267</v>
       </c>
       <c r="O311" s="1">
         <v>131681</v>
       </c>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:15">
       <c r="A312" s="1" t="s">
         <v>324</v>
       </c>
@@ -13153,19 +13725,19 @@
         <v>21</v>
       </c>
       <c r="L312" s="1">
-        <v>8.7183551999999997E-2</v>
+        <v>0.087183552</v>
       </c>
       <c r="M312" s="1">
         <v>0.03</v>
       </c>
       <c r="N312" s="1">
-        <v>1.604278E-3</v>
+        <v>0.001604278</v>
       </c>
       <c r="O312" s="1">
         <v>131677</v>
       </c>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:15">
       <c r="A313" s="1" t="s">
         <v>325</v>
       </c>
@@ -13194,19 +13766,19 @@
         <v>35</v>
       </c>
       <c r="L313" s="1">
-        <v>9.3623282000000002E-2</v>
+        <v>0.093623282</v>
       </c>
       <c r="M313" s="1">
-        <v>8.4000000000000005E-2</v>
+        <v>0.084</v>
       </c>
       <c r="N313" s="1">
-        <v>3.2196239999999999E-3</v>
+        <v>0.003219624</v>
       </c>
       <c r="O313" s="1">
         <v>131683</v>
       </c>
     </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:15">
       <c r="A314" s="1" t="s">
         <v>326</v>
       </c>
@@ -13235,19 +13807,19 @@
         <v>42</v>
       </c>
       <c r="L314" s="1">
-        <v>8.6099200000000001E-2</v>
+        <v>0.0860992</v>
       </c>
       <c r="M314" s="1">
-        <v>4.5999999999999999E-2</v>
+        <v>0.046</v>
       </c>
       <c r="N314" s="1">
-        <v>1.8039219999999999E-3</v>
+        <v>0.001803922</v>
       </c>
       <c r="O314" s="1">
         <v>131721</v>
       </c>
     </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:15">
       <c r="A315" s="1" t="s">
         <v>327</v>
       </c>
@@ -13276,19 +13848,19 @@
         <v>42</v>
       </c>
       <c r="L315" s="1">
-        <v>7.6847047000000002E-2</v>
+        <v>0.076847047</v>
       </c>
       <c r="M315" s="1">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="N315" s="1">
-        <v>3.4910430000000001E-3</v>
+        <v>0.003491043</v>
       </c>
       <c r="O315" s="1">
         <v>131705</v>
       </c>
     </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:15">
       <c r="A316" s="1" t="s">
         <v>328</v>
       </c>
@@ -13317,19 +13889,19 @@
         <v>29</v>
       </c>
       <c r="L316" s="1">
-        <v>9.0228094999999994E-2</v>
+        <v>0.090228095</v>
       </c>
       <c r="M316" s="1">
-        <v>0.10299999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="N316" s="1">
-        <v>3.2027359999999999E-3</v>
+        <v>0.003202736</v>
       </c>
       <c r="O316" s="1">
         <v>131709</v>
       </c>
     </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:15">
       <c r="A317" s="1" t="s">
         <v>329</v>
       </c>
@@ -13358,19 +13930,19 @@
         <v>20</v>
       </c>
       <c r="L317" s="1">
-        <v>6.5296627999999995E-2</v>
+        <v>0.065296628</v>
       </c>
       <c r="M317" s="1">
         <v>0.113</v>
       </c>
       <c r="N317" s="1">
-        <v>3.1697050000000001E-3</v>
+        <v>0.003169705</v>
       </c>
       <c r="O317" s="1">
         <v>131731</v>
       </c>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:15">
       <c r="A318" s="1" t="s">
         <v>330</v>
       </c>
@@ -13399,16 +13971,16 @@
         <v>20</v>
       </c>
       <c r="L318" s="1">
-        <v>7.4115455999999996E-2</v>
+        <v>0.074115456</v>
       </c>
       <c r="M318" s="1">
-        <v>0.23699999999999999</v>
+        <v>0.237</v>
       </c>
       <c r="N318" s="1">
-        <v>1.1909548000000001E-2</v>
-      </c>
-    </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.2">
+        <v>0.011909548</v>
+      </c>
+    </row>
+    <row r="319" spans="1:15">
       <c r="A319" s="1" t="s">
         <v>331</v>
       </c>
@@ -13437,19 +14009,19 @@
         <v>26</v>
       </c>
       <c r="L319" s="1">
-        <v>8.9860352000000004E-2</v>
+        <v>0.089860352</v>
       </c>
       <c r="M319" s="1">
         <v>0.06</v>
       </c>
       <c r="N319" s="1">
-        <v>2.5337839999999999E-3</v>
+        <v>0.002533784</v>
       </c>
       <c r="O319" s="1">
         <v>131593</v>
       </c>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:15">
       <c r="A320" s="1" t="s">
         <v>332</v>
       </c>
@@ -13478,19 +14050,19 @@
         <v>37</v>
       </c>
       <c r="L320" s="1">
-        <v>6.3784648999999999E-2</v>
+        <v>0.063784649</v>
       </c>
       <c r="M320" s="1">
         <v>0.49</v>
       </c>
       <c r="N320" s="1">
-        <v>2.6717556999999999E-2</v>
+        <v>0.026717557</v>
       </c>
       <c r="O320" s="1">
         <v>131611</v>
       </c>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:14">
       <c r="A321" s="1" t="s">
         <v>333</v>
       </c>
@@ -13507,16 +14079,16 @@
         <v>22</v>
       </c>
       <c r="L321" s="1">
-        <v>0.10031472600000001</v>
+        <v>0.100314726</v>
       </c>
       <c r="M321" s="1">
-        <v>5.1999999999999998E-2</v>
+        <v>0.052</v>
       </c>
       <c r="N321" s="1">
-        <v>1.7173049999999999E-3</v>
-      </c>
-    </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.2">
+        <v>0.001717305</v>
+      </c>
+    </row>
+    <row r="322" spans="1:14">
       <c r="A322" s="1" t="s">
         <v>334</v>
       </c>
@@ -13533,16 +14105,16 @@
         <v>10</v>
       </c>
       <c r="L322" s="1">
-        <v>6.6968801999999994E-2</v>
+        <v>0.066968802</v>
       </c>
       <c r="M322" s="1">
-        <v>0.78600000000000003</v>
+        <v>0.786</v>
       </c>
       <c r="N322" s="1">
-        <v>4.7492447E-2</v>
-      </c>
-    </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.2">
+        <v>0.047492447</v>
+      </c>
+    </row>
+    <row r="323" spans="1:14">
       <c r="A323" s="1" t="s">
         <v>335</v>
       </c>
@@ -13559,16 +14131,16 @@
         <v>21</v>
       </c>
       <c r="L323" s="1">
-        <v>8.1820768000000002E-2</v>
+        <v>0.081820768</v>
       </c>
       <c r="M323" s="1">
-        <v>9.1999999999999998E-2</v>
+        <v>0.092</v>
       </c>
       <c r="N323" s="1">
-        <v>3.1988870000000001E-3</v>
-      </c>
-    </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.2">
+        <v>0.003198887</v>
+      </c>
+    </row>
+    <row r="324" spans="1:14">
       <c r="A324" s="1" t="s">
         <v>336</v>
       </c>
@@ -13588,16 +14160,16 @@
         <v>20</v>
       </c>
       <c r="L324" s="1">
-        <v>6.4213246000000002E-2</v>
+        <v>0.064213246</v>
       </c>
       <c r="M324" s="1">
         <v>1.052</v>
       </c>
       <c r="N324" s="1">
-        <v>5.1619234999999999E-2</v>
-      </c>
-    </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.2">
+        <v>0.051619235</v>
+      </c>
+    </row>
+    <row r="325" spans="1:14">
       <c r="A325" s="1" t="s">
         <v>337</v>
       </c>
@@ -13626,7 +14198,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:14">
       <c r="A326" s="1" t="s">
         <v>338</v>
       </c>
@@ -13655,7 +14227,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:14">
       <c r="A327" s="1" t="s">
         <v>339</v>
       </c>
@@ -13666,7 +14238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:14">
       <c r="A328" s="1" t="s">
         <v>340</v>
       </c>
@@ -13677,7 +14249,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:14">
       <c r="A329" s="1" t="s">
         <v>341</v>
       </c>
@@ -13706,7 +14278,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:14">
       <c r="A330" s="1" t="s">
         <v>342</v>
       </c>
@@ -13735,7 +14307,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:14">
       <c r="A331" s="1" t="s">
         <v>343</v>
       </c>
@@ -13764,7 +14336,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:14">
       <c r="A332" s="1" t="s">
         <v>344</v>
       </c>
@@ -13793,7 +14365,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:14">
       <c r="A333" s="1" t="s">
         <v>345</v>
       </c>
@@ -13822,7 +14394,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:14">
       <c r="A334" s="1" t="s">
         <v>346</v>
       </c>
@@ -13851,7 +14423,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:14">
       <c r="A335" s="1" t="s">
         <v>347</v>
       </c>
@@ -13880,7 +14452,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:14">
       <c r="A336" s="1" t="s">
         <v>348</v>
       </c>
@@ -13909,7 +14481,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:9">
       <c r="A337" s="1" t="s">
         <v>349</v>
       </c>
@@ -13938,7 +14510,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:9">
       <c r="A338" s="1" t="s">
         <v>350</v>
       </c>
@@ -13967,7 +14539,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:9">
       <c r="A339" s="1" t="s">
         <v>351</v>
       </c>
@@ -13996,7 +14568,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:9">
       <c r="A340" s="1" t="s">
         <v>352</v>
       </c>
@@ -14025,7 +14597,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:9">
       <c r="A341" s="1" t="s">
         <v>353</v>
       </c>
@@ -14054,7 +14626,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:9">
       <c r="A342" s="1" t="s">
         <v>354</v>
       </c>
@@ -14083,7 +14655,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:9">
       <c r="A343" s="1" t="s">
         <v>355</v>
       </c>
@@ -14094,7 +14666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:9">
       <c r="A344" s="1" t="s">
         <v>356</v>
       </c>
@@ -14123,7 +14695,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:9">
       <c r="A345" s="1" t="s">
         <v>357</v>
       </c>
@@ -14152,7 +14724,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:9">
       <c r="A346" s="1" t="s">
         <v>358</v>
       </c>
@@ -14181,7 +14753,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:9">
       <c r="A347" s="1" t="s">
         <v>359</v>
       </c>
@@ -14192,7 +14764,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:9">
       <c r="A348" s="1" t="s">
         <v>360</v>
       </c>
@@ -14221,7 +14793,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:9">
       <c r="A349" s="1" t="s">
         <v>361</v>
       </c>
@@ -14235,7 +14807,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:9">
       <c r="A350" s="1" t="s">
         <v>362</v>
       </c>
@@ -14264,7 +14836,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:9">
       <c r="A351" s="1" t="s">
         <v>363</v>
       </c>
@@ -14293,7 +14865,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:9">
       <c r="A352" s="1" t="s">
         <v>364</v>
       </c>
@@ -14322,7 +14894,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:9">
       <c r="A353" s="1" t="s">
         <v>365</v>
       </c>
@@ -14351,7 +14923,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:9">
       <c r="A354" s="1" t="s">
         <v>366</v>
       </c>
@@ -14380,7 +14952,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:9">
       <c r="A355" s="1" t="s">
         <v>367</v>
       </c>
@@ -14409,7 +14981,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:9">
       <c r="A356" s="1" t="s">
         <v>368</v>
       </c>
@@ -14438,7 +15010,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:9">
       <c r="A357" s="1" t="s">
         <v>369</v>
       </c>
@@ -14467,7 +15039,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:9">
       <c r="A358" s="1" t="s">
         <v>370</v>
       </c>
@@ -14496,7 +15068,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:9">
       <c r="A359" s="1" t="s">
         <v>371</v>
       </c>
@@ -14525,7 +15097,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:9">
       <c r="A360" s="1" t="s">
         <v>372</v>
       </c>
@@ -14554,7 +15126,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:9">
       <c r="A361" s="1" t="s">
         <v>373</v>
       </c>
@@ -14584,7 +15156,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>